--- a/EquipmentList2026.xlsx
+++ b/EquipmentList2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JCDC\Desktop\JCDC-main\JCDC-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3B5FE5C3-F688-4365-8651-CE8B29DB0C1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AA8CF05-8263-48C4-A1A9-36B970219B81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B941218B-1749-4563-9A81-514A1DFAB1CE}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Supplier Equipment" sheetId="5" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Supplier Equipment'!$A$1:$M$199</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Supplier Equipment'!$A$1:$M$198</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1527" uniqueCount="550">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1550" uniqueCount="551">
   <si>
     <t>FLEET CODE</t>
   </si>
@@ -201,9 +201,6 @@
     <t>MUHAMMAD ASLAM MUHAMMAD SHARIF</t>
   </si>
   <si>
-    <t>056 7748401</t>
-  </si>
-  <si>
     <t>C050</t>
   </si>
   <si>
@@ -250,30 +247,6 @@
   </si>
   <si>
     <t>Shahzib Liaqat</t>
-  </si>
-  <si>
-    <t>Forklift</t>
-  </si>
-  <si>
-    <t>C141</t>
-  </si>
-  <si>
-    <t>HHKHFTO8CD0001047</t>
-  </si>
-  <si>
-    <t>2025.07.31</t>
-  </si>
-  <si>
-    <t>MUHAMMAD ALI SHAH ALLAH KHAN</t>
-  </si>
-  <si>
-    <t>HALA Est.</t>
-  </si>
-  <si>
-    <t>2025.08.02</t>
-  </si>
-  <si>
-    <t>WAQAS AHMED GULISTAN</t>
   </si>
   <si>
     <t>C146</t>
@@ -545,9 +518,6 @@
 MUHAMMAD RIAZ </t>
   </si>
   <si>
-    <t>MUHAMMAD AFZAL</t>
-  </si>
-  <si>
     <t>Whole Stadium/Lifting Team</t>
   </si>
   <si>
@@ -866,9 +836,6 @@
     <t>26/11/2025</t>
   </si>
   <si>
-    <t>QAMRAIZ KHAN MUHAMMAD IDREES KHAN</t>
-  </si>
-  <si>
     <t>Water Tanker(18000LTR)</t>
   </si>
   <si>
@@ -1538,6 +1505,9 @@
     <t>Zone 1</t>
   </si>
   <si>
+    <t>Shaju</t>
+  </si>
+  <si>
     <t>邓群力</t>
   </si>
   <si>
@@ -1680,6 +1650,39 @@
   </si>
   <si>
     <t>PHULIL KHAN AMIR</t>
+  </si>
+  <si>
+    <t>Tower Crane</t>
+  </si>
+  <si>
+    <t>1012TC01701828</t>
+  </si>
+  <si>
+    <t>1012TC01702382</t>
+  </si>
+  <si>
+    <t>Boom Truck</t>
+  </si>
+  <si>
+    <t>2640 EDA</t>
+  </si>
+  <si>
+    <t>2641 EDA</t>
+  </si>
+  <si>
+    <t>ANWAR KHAN IMAM DIN</t>
+  </si>
+  <si>
+    <t>JCDC</t>
+  </si>
+  <si>
+    <t>PMV</t>
+  </si>
+  <si>
+    <t>RAKIB MIA</t>
+  </si>
+  <si>
+    <t>FAZAL WAHID</t>
   </si>
 </sst>
 </file>
@@ -1816,7 +1819,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1889,12 +1892,25 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 3" xfId="1" xr:uid="{F3517B68-4488-4A8F-BD09-41B7BB3778AD}"/>
   </cellStyles>
   <dxfs count="37">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -2171,16 +2187,6 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
@@ -2598,7 +2604,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:R413"/>
+  <dimension ref="A1:R412"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.28515625" style="6" customWidth="1"/>
@@ -2621,40 +2627,40 @@
         <v>1</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>449</v>
+        <v>438</v>
       </c>
       <c r="C1" s="7" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>450</v>
+        <v>439</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>451</v>
+        <v>440</v>
       </c>
       <c r="F1" s="7" t="s">
         <v>1</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>452</v>
+        <v>441</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>453</v>
+        <v>442</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>454</v>
+        <v>443</v>
       </c>
       <c r="J1" s="9" t="s">
-        <v>455</v>
+        <v>444</v>
       </c>
       <c r="K1" s="7" t="s">
-        <v>456</v>
+        <v>445</v>
       </c>
       <c r="L1" s="7" t="s">
-        <v>457</v>
+        <v>446</v>
       </c>
       <c r="M1" s="7" t="s">
-        <v>458</v>
+        <v>447</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
@@ -2662,22 +2668,22 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>15</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="H2" s="1">
         <v>2559084500</v>
@@ -2686,16 +2692,16 @@
         <v>554190144</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="K2" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
@@ -2703,22 +2709,22 @@
         <v>1</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>48</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="H3" s="3">
         <v>2585508274</v>
@@ -2727,16 +2733,16 @@
         <v>572451793</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="K3" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
@@ -2744,22 +2750,22 @@
         <v>1</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>15</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="H4" s="3">
         <v>2587342151</v>
@@ -2768,16 +2774,16 @@
         <v>571659236</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="K4" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
@@ -2785,40 +2791,40 @@
         <v>1</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="G5" s="3" t="s">
         <v>89</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>98</v>
       </c>
       <c r="H5" s="3">
         <v>2587587623</v>
       </c>
       <c r="I5" s="3">
-        <v>57346135</v>
+        <v>573461350</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="K5" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
@@ -2826,22 +2832,22 @@
         <v>1</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="H6" s="3">
         <v>2585506872</v>
@@ -2850,40 +2856,40 @@
         <v>572869101</v>
       </c>
       <c r="J6" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="K6" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="L6" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="K6" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="L6" s="3" t="s">
-        <v>103</v>
-      </c>
       <c r="M6" s="1" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
-        <f t="shared" ref="A7:A70" si="0">A6+1</f>
+        <f t="shared" ref="A7:G68" si="0">A6+1</f>
         <v>2</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>15</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="H7" s="3">
         <v>2528123843</v>
@@ -2892,16 +2898,16 @@
         <v>562365726</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="K7" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
@@ -2910,40 +2916,40 @@
         <v>3</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>15</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="H8" s="3">
         <v>2571347232</v>
       </c>
       <c r="I8" s="3">
-        <v>1</v>
+        <v>595095632</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="K8" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
@@ -2952,20 +2958,20 @@
         <v>4</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>15</v>
       </c>
       <c r="F9" s="3"/>
       <c r="G9" s="3" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="H9" s="3">
         <v>2587755949</v>
@@ -2974,16 +2980,16 @@
         <v>551524713</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="K9" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
@@ -2992,22 +2998,22 @@
         <v>5</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>48</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="H10" s="3">
         <v>2604075503</v>
@@ -3016,21 +3022,21 @@
         <v>536871868</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="K10" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="A11" si="1">A10+1</f>
         <v>6</v>
       </c>
       <c r="B11" s="3" t="s">
@@ -3064,15 +3070,15 @@
         <v>9</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="A12" si="2">A11+1</f>
         <v>7</v>
       </c>
       <c r="B12" s="3" t="s">
@@ -3106,124 +3112,124 @@
         <v>9</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="A13" si="3">A12+1</f>
         <v>8</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>75</v>
+        <v>51</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>76</v>
+        <v>52</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>15</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>78</v>
+        <v>54</v>
       </c>
       <c r="H13" s="3">
-        <v>2539417143</v>
+        <v>2574339483</v>
       </c>
       <c r="I13" s="3">
-        <v>593695046</v>
+        <v>546985679</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>79</v>
+        <v>43</v>
       </c>
       <c r="K13" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
     </row>
     <row r="14" spans="1:13" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="A14" si="4">A13+1</f>
         <v>9</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>75</v>
+        <v>51</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>76</v>
+        <v>52</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>48</v>
+        <v>10</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>81</v>
+        <v>56</v>
       </c>
       <c r="H14" s="3">
-        <v>2602039030</v>
+        <v>2613249842</v>
       </c>
       <c r="I14" s="3">
-        <v>1</v>
+        <v>567748401</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>79</v>
+        <v>43</v>
       </c>
       <c r="K14" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
     </row>
     <row r="15" spans="1:13" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="A15" si="5">A14+1</f>
         <v>10</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>50</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>15</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="H15" s="3">
-        <v>2574339483</v>
+        <v>2587996261</v>
       </c>
       <c r="I15" s="3">
-        <v>546985679</v>
+        <v>574548286</v>
       </c>
       <c r="J15" s="3" t="s">
         <v>43</v>
@@ -3232,40 +3238,40 @@
         <v>9</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="16" spans="1:13" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="A16" si="6">A15+1</f>
         <v>11</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>50</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="H16" s="3">
-        <v>2613249842</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>57</v>
+        <v>2597417209</v>
+      </c>
+      <c r="I16" s="3">
+        <v>545841253</v>
       </c>
       <c r="J16" s="3" t="s">
         <v>43</v>
@@ -3274,40 +3280,40 @@
         <v>9</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
     </row>
     <row r="17" spans="1:13" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="A17" si="7">A16+1</f>
         <v>12</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="H17" s="3">
-        <v>2587996261</v>
+        <v>2562204723</v>
       </c>
       <c r="I17" s="3">
-        <v>574548286</v>
+        <v>541601873</v>
       </c>
       <c r="J17" s="3" t="s">
         <v>43</v>
@@ -3316,680 +3322,680 @@
         <v>9</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
     </row>
     <row r="18" spans="1:13" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="A18" si="8">A17+1</f>
         <v>13</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="H18" s="3">
-        <v>2597417209</v>
-      </c>
-      <c r="I18" s="3">
-        <v>545841253</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>43</v>
+      <c r="B18" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="H18" s="1">
+        <v>2523182802</v>
+      </c>
+      <c r="I18" s="1">
+        <v>592490129</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>77</v>
       </c>
       <c r="K18" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>188</v>
+      <c r="L18" s="1" t="s">
+        <v>144</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>193</v>
+        <v>145</v>
       </c>
     </row>
     <row r="19" spans="1:13" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="A19" si="9">A18+1</f>
         <v>14</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>64</v>
+        <v>27</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>5</v>
+        <v>48</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="H19" s="3">
-        <v>2562204723</v>
+        <v>2603868361</v>
       </c>
       <c r="I19" s="3">
-        <v>541601873</v>
+        <v>551898837</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>43</v>
+        <v>77</v>
       </c>
       <c r="K19" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
     </row>
     <row r="20" spans="1:13" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="A20" si="10">A19+1</f>
         <v>15</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B20" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="H20" s="1">
-        <v>2523182802</v>
-      </c>
-      <c r="I20" s="1">
-        <v>592490129</v>
-      </c>
-      <c r="J20" s="1" t="s">
-        <v>86</v>
+      <c r="C20" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="H20" s="3">
+        <v>2545224251</v>
+      </c>
+      <c r="I20" s="3">
+        <v>535631060</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>77</v>
       </c>
       <c r="K20" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="L20" s="1" t="s">
-        <v>153</v>
+      <c r="L20" s="3" t="s">
+        <v>181</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>154</v>
+        <v>182</v>
       </c>
     </row>
     <row r="21" spans="1:13" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="A21" si="11">A20+1</f>
         <v>16</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="H21" s="3">
-        <v>2603868361</v>
-      </c>
-      <c r="I21" s="3">
-        <v>551898837</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>86</v>
+      <c r="B21" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="D21" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="G21" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="H21" s="20">
+        <v>2588084042</v>
+      </c>
+      <c r="I21" s="20">
+        <v>592795913</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="K21" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="M21" s="1" t="s">
-        <v>194</v>
+      <c r="L21" s="20" t="s">
+        <v>525</v>
+      </c>
+      <c r="M21" s="23" t="s">
+        <v>524</v>
       </c>
     </row>
     <row r="22" spans="1:13" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="A22" si="12">A21+1</f>
         <v>17</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="H22" s="3">
-        <v>2545224251</v>
-      </c>
-      <c r="I22" s="3">
-        <v>535631060</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>86</v>
+      <c r="B22" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H22" s="1">
+        <v>2588084042</v>
+      </c>
+      <c r="I22" s="1">
+        <v>592795913</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>33</v>
       </c>
       <c r="K22" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>191</v>
+      <c r="L22" s="1" t="s">
+        <v>144</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>192</v>
+        <v>145</v>
       </c>
     </row>
     <row r="23" spans="1:13" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="A23" si="13">A22+1</f>
         <v>18</v>
       </c>
-      <c r="B23" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="D23" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="G23" s="20" t="s">
-        <v>32</v>
-      </c>
-      <c r="H23" s="20">
-        <v>2588084042</v>
-      </c>
-      <c r="I23" s="20">
-        <v>592795913</v>
-      </c>
-      <c r="J23" s="1" t="s">
-        <v>24</v>
+      <c r="B23" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="H23" s="3">
+        <v>2534900234</v>
+      </c>
+      <c r="I23" s="3">
+        <v>575295148</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>43</v>
       </c>
       <c r="K23" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="L23" s="20" t="s">
-        <v>535</v>
-      </c>
-      <c r="M23" s="23" t="s">
-        <v>534</v>
+      <c r="L23" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="M23" s="1" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="24" spans="1:13" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="A24" si="14">A23+1</f>
         <v>19</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>30</v>
+        <v>143</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="H24" s="1">
-        <v>2588084042</v>
+        <v>2597412648</v>
       </c>
       <c r="I24" s="1">
-        <v>592795913</v>
+        <v>572070254</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="K24" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
     </row>
     <row r="25" spans="1:13" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="A25" si="15">A24+1</f>
         <v>20</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>69</v>
+        <v>19</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>70</v>
+        <v>25</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>71</v>
+        <v>21</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>72</v>
+        <v>22</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>73</v>
+        <v>26</v>
       </c>
       <c r="H25" s="3">
-        <v>2534900234</v>
+        <v>2597412234</v>
       </c>
       <c r="I25" s="3">
-        <v>575295148</v>
+        <v>572076705</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="K25" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="M25" s="1" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
     </row>
     <row r="26" spans="1:13" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="A26" si="16">A25+1</f>
         <v>21</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>19</v>
+        <v>148</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>152</v>
+        <v>40</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="H26" s="1">
-        <v>2597412648</v>
+        <v>2544315373</v>
       </c>
       <c r="I26" s="1">
-        <v>572070254</v>
+        <v>510107382</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="K26" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
     </row>
     <row r="27" spans="1:13" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="A27" si="17">A26+1</f>
         <v>22</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="H27" s="3">
-        <v>2597412234</v>
-      </c>
-      <c r="I27" s="3">
-        <v>572076705</v>
-      </c>
-      <c r="J27" s="3" t="s">
-        <v>24</v>
+      <c r="B27" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="H27" s="1">
+        <v>2521125969</v>
+      </c>
+      <c r="I27" s="1">
+        <v>505634856</v>
+      </c>
+      <c r="J27" s="1" t="s">
+        <v>138</v>
       </c>
       <c r="K27" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="L27" s="3" t="s">
-        <v>196</v>
+      <c r="L27" s="1" t="s">
+        <v>150</v>
       </c>
       <c r="M27" s="1" t="s">
-        <v>195</v>
+        <v>151</v>
       </c>
     </row>
     <row r="28" spans="1:13" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="A28" si="18">A27+1</f>
         <v>23</v>
       </c>
       <c r="B28" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F28" s="1"/>
+      <c r="G28" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="H28" s="1">
+        <v>2612850921</v>
+      </c>
+      <c r="I28" s="1">
+        <v>542103501</v>
+      </c>
+      <c r="J28" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="K28" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="L28" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="M28" s="1" t="s">
         <v>157</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G28" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="H28" s="1">
-        <v>2544315373</v>
-      </c>
-      <c r="I28" s="1">
-        <v>510107382</v>
-      </c>
-      <c r="J28" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="K28" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="L28" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="M28" s="1" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="29" spans="1:13" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="A29" si="19">A28+1</f>
         <v>24</v>
       </c>
-      <c r="B29" s="1" t="s">
+      <c r="B29" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C29" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="G29" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="H29" s="1">
-        <v>2521125969</v>
-      </c>
-      <c r="I29" s="1">
-        <v>505634856</v>
-      </c>
-      <c r="J29" s="1" t="s">
-        <v>147</v>
+      <c r="C29" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="H29" s="3">
+        <v>2398556064</v>
+      </c>
+      <c r="I29" s="3">
+        <v>590536531</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>77</v>
       </c>
       <c r="K29" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="L29" s="1" t="s">
-        <v>159</v>
+      <c r="L29" s="3" t="s">
+        <v>162</v>
       </c>
       <c r="M29" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
     </row>
     <row r="30" spans="1:13" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="A30" si="20">A29+1</f>
         <v>25</v>
       </c>
-      <c r="B30" s="1" t="s">
+      <c r="B30" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C30" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="D30" s="1" t="s">
+      <c r="C30" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="G30" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="E30" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F30" s="1"/>
-      <c r="G30" s="1" t="s">
+      <c r="H30" s="3">
+        <v>2538148368</v>
+      </c>
+      <c r="I30" s="3">
+        <v>555395683</v>
+      </c>
+      <c r="J30" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="K30" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="L30" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="H30" s="1">
-        <v>2612850921</v>
-      </c>
-      <c r="I30" s="1">
-        <v>542103501</v>
-      </c>
-      <c r="J30" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="K30" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="L30" s="1" t="s">
-        <v>165</v>
-      </c>
       <c r="M30" s="1" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
     </row>
     <row r="31" spans="1:13" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="A31" si="21">A30+1</f>
         <v>26</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>138</v>
+        <v>125</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>139</v>
+        <v>126</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>48</v>
+        <v>15</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>140</v>
+        <v>127</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="H31" s="3">
-        <v>2398556064</v>
+        <v>2338642268</v>
       </c>
       <c r="I31" s="3">
-        <v>590536531</v>
+        <v>575295148</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="K31" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L31" s="3" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="M31" s="1" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
     </row>
     <row r="32" spans="1:13" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="A32" si="22">A31+1</f>
         <v>27</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>138</v>
+        <v>125</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>139</v>
+        <v>126</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>142</v>
+        <v>127</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>170</v>
+        <v>550</v>
       </c>
       <c r="H32" s="3">
-        <v>2538148368</v>
+        <v>2575744400</v>
       </c>
       <c r="I32" s="3">
-        <v>1</v>
+        <v>530981238</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="K32" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L32" s="3" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="M32" s="1" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
     </row>
     <row r="33" spans="1:13" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="A33" si="23">A32+1</f>
         <v>28</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>134</v>
+        <v>13</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>135</v>
+        <v>14</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>15</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>136</v>
+        <v>6</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>137</v>
+        <v>16</v>
       </c>
       <c r="H33" s="3">
-        <v>2338642248</v>
+        <v>2568925875</v>
       </c>
       <c r="I33" s="3">
-        <v>1</v>
+        <v>593017078</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>86</v>
+        <v>17</v>
       </c>
       <c r="K33" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L33" s="3" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="M33" s="1" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
     </row>
     <row r="34" spans="1:13" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
@@ -4001,37 +4007,37 @@
         <v>12</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>134</v>
+        <v>13</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>135</v>
+        <v>14</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>48</v>
+        <v>10</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>136</v>
+        <v>6</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>171</v>
+        <v>18</v>
       </c>
       <c r="H34" s="3">
-        <v>2567521543</v>
+        <v>2609856642</v>
       </c>
       <c r="I34" s="3">
-        <v>530229346</v>
+        <v>595094746</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>86</v>
+        <v>17</v>
       </c>
       <c r="K34" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L34" s="3" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="M34" s="1" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
     </row>
     <row r="35" spans="1:13" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
@@ -4043,37 +4049,37 @@
         <v>12</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>13</v>
+        <v>103</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>14</v>
+        <v>104</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>6</v>
+        <v>102</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>16</v>
+        <v>105</v>
       </c>
       <c r="H35" s="3">
-        <v>2568925875</v>
+        <v>2208199840</v>
       </c>
       <c r="I35" s="3">
-        <v>593017078</v>
+        <v>538462770</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>17</v>
+        <v>106</v>
       </c>
       <c r="K35" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L35" s="3" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="M35" s="1" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
     </row>
     <row r="36" spans="1:13" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
@@ -4085,37 +4091,37 @@
         <v>12</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>13</v>
+        <v>103</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>14</v>
+        <v>104</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>6</v>
+        <v>102</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>18</v>
+        <v>107</v>
       </c>
       <c r="H36" s="3">
-        <v>2609856642</v>
+        <v>2392654550</v>
       </c>
       <c r="I36" s="3">
-        <v>1</v>
+        <v>568104968</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>17</v>
+        <v>106</v>
       </c>
       <c r="K36" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L36" s="3" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="M36" s="1" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
     </row>
     <row r="37" spans="1:13" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
@@ -4127,37 +4133,37 @@
         <v>12</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>112</v>
+        <v>34</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>113</v>
+        <v>35</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>111</v>
+        <v>36</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>114</v>
+        <v>37</v>
       </c>
       <c r="H37" s="3">
-        <v>2208199840</v>
+        <v>2617777137</v>
       </c>
       <c r="I37" s="3">
-        <v>538462770</v>
+        <v>565446173</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>115</v>
+        <v>38</v>
       </c>
       <c r="K37" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L37" s="3" t="s">
-        <v>174</v>
+        <v>188</v>
       </c>
       <c r="M37" s="1" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
     </row>
     <row r="38" spans="1:13" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
@@ -4169,37 +4175,37 @@
         <v>12</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>112</v>
+        <v>44</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>113</v>
+        <v>45</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>15</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>111</v>
+        <v>46</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>116</v>
+        <v>47</v>
       </c>
       <c r="H38" s="3">
-        <v>2392654550</v>
+        <v>2282718077</v>
       </c>
       <c r="I38" s="3">
-        <v>568104968</v>
+        <v>505836391</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>115</v>
+        <v>38</v>
       </c>
       <c r="K38" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L38" s="3" t="s">
-        <v>174</v>
+        <v>192</v>
       </c>
       <c r="M38" s="1" t="s">
-        <v>175</v>
+        <v>191</v>
       </c>
     </row>
     <row r="39" spans="1:13" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
@@ -4211,25 +4217,25 @@
         <v>12</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>5</v>
+        <v>48</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="H39" s="3">
-        <v>2617777137</v>
+        <v>2511610913</v>
       </c>
       <c r="I39" s="3">
-        <v>565446173</v>
+        <v>552849128</v>
       </c>
       <c r="J39" s="3" t="s">
         <v>38</v>
@@ -4238,10 +4244,10 @@
         <v>9</v>
       </c>
       <c r="L39" s="3" t="s">
-        <v>198</v>
+        <v>166</v>
       </c>
       <c r="M39" s="1" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
     </row>
     <row r="40" spans="1:13" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
@@ -4252,38 +4258,34 @@
       <c r="B40" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C40" s="3" t="s">
-        <v>44</v>
-      </c>
+      <c r="C40" s="3"/>
       <c r="D40" s="3" t="s">
-        <v>45</v>
+        <v>154</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F40" s="3" t="s">
-        <v>46</v>
-      </c>
+      <c r="F40" s="3"/>
       <c r="G40" s="3" t="s">
-        <v>47</v>
+        <v>155</v>
       </c>
       <c r="H40" s="3">
-        <v>2282718077</v>
+        <v>2538063906</v>
       </c>
       <c r="I40" s="3">
-        <v>505836391</v>
+        <v>583607768</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>38</v>
+        <v>138</v>
       </c>
       <c r="K40" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L40" s="3" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="M40" s="1" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
     </row>
     <row r="41" spans="1:13" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
@@ -4294,38 +4296,36 @@
       <c r="B41" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C41" s="3" t="s">
-        <v>44</v>
-      </c>
+      <c r="C41" s="3"/>
       <c r="D41" s="3" t="s">
-        <v>45</v>
+        <v>158</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>48</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>46</v>
+        <v>160</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>49</v>
+        <v>159</v>
       </c>
       <c r="H41" s="3">
-        <v>2511610913</v>
+        <v>2400283434</v>
       </c>
       <c r="I41" s="3">
-        <v>552849128</v>
+        <v>595161368</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>38</v>
+        <v>138</v>
       </c>
       <c r="K41" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L41" s="3" t="s">
-        <v>176</v>
+        <v>189</v>
       </c>
       <c r="M41" s="1" t="s">
-        <v>203</v>
+        <v>190</v>
       </c>
     </row>
     <row r="42" spans="1:13" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
@@ -4336,34 +4336,38 @@
       <c r="B42" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C42" s="3"/>
+      <c r="C42" s="3" t="s">
+        <v>139</v>
+      </c>
       <c r="D42" s="3" t="s">
-        <v>163</v>
+        <v>140</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F42" s="3"/>
+      <c r="F42" s="3" t="s">
+        <v>136</v>
+      </c>
       <c r="G42" s="3" t="s">
-        <v>164</v>
+        <v>141</v>
       </c>
       <c r="H42" s="3">
-        <v>2538063906</v>
+        <v>2609633769</v>
       </c>
       <c r="I42" s="3">
-        <v>583607768</v>
+        <v>538297877</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="K42" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L42" s="3" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="M42" s="1" t="s">
-        <v>200</v>
+        <v>190</v>
       </c>
     </row>
     <row r="43" spans="1:13" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
@@ -4376,34 +4380,34 @@
       </c>
       <c r="C43" s="3"/>
       <c r="D43" s="3" t="s">
-        <v>167</v>
+        <v>414</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>169</v>
+        <v>15</v>
+      </c>
+      <c r="F43" s="18">
+        <v>46035</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>168</v>
+        <v>415</v>
       </c>
       <c r="H43" s="3">
-        <v>2400283434</v>
+        <v>2625343054</v>
       </c>
       <c r="I43" s="3">
-        <v>59161368</v>
+        <v>573352861</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="K43" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L43" s="3" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="M43" s="1" t="s">
-        <v>200</v>
+        <v>190</v>
       </c>
     </row>
     <row r="44" spans="1:13" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
@@ -4414,38 +4418,36 @@
       <c r="B44" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C44" s="3" t="s">
-        <v>148</v>
-      </c>
+      <c r="C44" s="3"/>
       <c r="D44" s="3" t="s">
-        <v>149</v>
+        <v>414</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>145</v>
+        <v>48</v>
+      </c>
+      <c r="F44" s="18">
+        <v>46035</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>150</v>
+        <v>416</v>
       </c>
       <c r="H44" s="3">
-        <v>2609633769</v>
+        <v>2605767538</v>
       </c>
       <c r="I44" s="3">
-        <v>538297877</v>
+        <v>556971913</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="K44" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L44" s="3" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="M44" s="1" t="s">
-        <v>200</v>
+        <v>190</v>
       </c>
     </row>
     <row r="45" spans="1:13" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
@@ -4454,118 +4456,118 @@
         <v>40</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>12</v>
+        <v>194</v>
       </c>
       <c r="C45" s="3"/>
-      <c r="D45" s="3" t="s">
-        <v>425</v>
+      <c r="D45" s="3">
+        <v>6011252607</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="F45" s="18">
-        <v>46035</v>
+        <v>5</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>198</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>426</v>
+        <v>195</v>
       </c>
       <c r="H45" s="3">
-        <v>2625343054</v>
+        <v>2406532057</v>
       </c>
       <c r="I45" s="3">
-        <v>573352861</v>
+        <v>572708132</v>
       </c>
       <c r="J45" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="K45" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="L45" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="M45" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="K45" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="L45" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="M45" s="1" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="46" spans="1:13" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="46" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>12</v>
+        <v>194</v>
       </c>
       <c r="C46" s="3"/>
-      <c r="D46" s="3" t="s">
-        <v>425</v>
+      <c r="D46" s="3">
+        <v>6011252607</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F46" s="18">
-        <v>46035</v>
+        <v>10</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>199</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>427</v>
+        <v>196</v>
       </c>
       <c r="H46" s="3">
-        <v>2605767538</v>
+        <v>2619027424</v>
       </c>
       <c r="I46" s="3">
-        <v>556971913</v>
+        <v>508401823</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>147</v>
+        <v>197</v>
       </c>
       <c r="K46" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L46" s="3" t="s">
-        <v>199</v>
+        <v>395</v>
       </c>
       <c r="M46" s="1" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="47" spans="1:13" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <f t="shared" si="0"/>
         <v>42</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="C47" s="3"/>
-      <c r="D47" s="3">
-        <v>6011252607</v>
+      <c r="D47" s="3" t="s">
+        <v>200</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>5</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="H47" s="3">
-        <v>2406532057</v>
+        <v>2619027085</v>
       </c>
       <c r="I47" s="3">
-        <v>572708132</v>
+        <v>568654896</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="K47" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L47" s="3" t="s">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="M47" s="1" t="s">
-        <v>156</v>
+        <v>399</v>
       </c>
     </row>
     <row r="48" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4574,38 +4576,38 @@
         <v>43</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="C48" s="3"/>
-      <c r="D48" s="3">
-        <v>6011252607</v>
+      <c r="D48" s="3" t="s">
+        <v>200</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="H48" s="3">
-        <v>2619027424</v>
+        <v>2619026988</v>
       </c>
       <c r="I48" s="3">
-        <v>508401823</v>
+        <v>559537930</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="K48" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L48" s="3" t="s">
-        <v>406</v>
+        <v>395</v>
       </c>
       <c r="M48" s="1" t="s">
-        <v>405</v>
+        <v>394</v>
       </c>
     </row>
     <row r="49" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4614,26 +4616,26 @@
         <v>44</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="C49" s="3"/>
       <c r="D49" s="3" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>5</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="H49" s="3">
-        <v>2619027085</v>
+        <v>2533248643</v>
       </c>
       <c r="I49" s="3">
-        <v>568654896</v>
+        <v>582378470</v>
       </c>
       <c r="J49" s="3" t="s">
         <v>207</v>
@@ -4642,10 +4644,10 @@
         <v>9</v>
       </c>
       <c r="L49" s="3" t="s">
-        <v>431</v>
+        <v>422</v>
       </c>
       <c r="M49" s="1" t="s">
-        <v>410</v>
+        <v>423</v>
       </c>
     </row>
     <row r="50" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4654,38 +4656,38 @@
         <v>45</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="C50" s="3"/>
       <c r="D50" s="3" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="H50" s="3">
-        <v>2619026988</v>
+        <v>2619027523</v>
       </c>
       <c r="I50" s="3">
-        <v>559537930</v>
+        <v>534265668</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="K50" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L50" s="3" t="s">
-        <v>406</v>
+        <v>424</v>
       </c>
       <c r="M50" s="1" t="s">
-        <v>405</v>
+        <v>427</v>
       </c>
     </row>
     <row r="51" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4694,38 +4696,38 @@
         <v>46</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="C51" s="3"/>
       <c r="D51" s="3" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>5</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>220</v>
+        <v>235</v>
       </c>
       <c r="H51" s="3">
-        <v>2533248643</v>
+        <v>2580279038</v>
       </c>
       <c r="I51" s="3">
-        <v>582378470</v>
+        <v>508864254</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="K51" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L51" s="3" t="s">
-        <v>433</v>
+        <v>390</v>
       </c>
       <c r="M51" s="1" t="s">
-        <v>434</v>
+        <v>421</v>
       </c>
     </row>
     <row r="52" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4734,38 +4736,38 @@
         <v>47</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>204</v>
+        <v>215</v>
       </c>
       <c r="C52" s="3"/>
       <c r="D52" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F52" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="G52" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="G52" s="3" t="s">
-        <v>219</v>
-      </c>
       <c r="H52" s="3">
-        <v>2619027523</v>
+        <v>2619027481</v>
       </c>
       <c r="I52" s="3">
-        <v>534265668</v>
+        <v>564940249</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="K52" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L52" s="3" t="s">
-        <v>435</v>
+        <v>400</v>
       </c>
       <c r="M52" s="1" t="s">
-        <v>438</v>
+        <v>401</v>
       </c>
     </row>
     <row r="53" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4774,38 +4776,38 @@
         <v>48</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="C53" s="3"/>
       <c r="D53" s="3" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>245</v>
+        <v>221</v>
       </c>
       <c r="H53" s="3">
-        <v>2580279038</v>
+        <v>2401619040</v>
       </c>
       <c r="I53" s="3">
-        <v>508864254</v>
+        <v>570393603</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>224</v>
+        <v>197</v>
       </c>
       <c r="K53" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L53" s="3" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="M53" s="1" t="s">
-        <v>432</v>
+        <v>394</v>
       </c>
     </row>
     <row r="54" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4814,38 +4816,36 @@
         <v>49</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="C54" s="3"/>
       <c r="D54" s="3" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F54" s="3" t="s">
-        <v>227</v>
-      </c>
+      <c r="F54" s="3"/>
       <c r="G54" s="3" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="H54" s="3">
-        <v>2619027481</v>
+        <v>2336749334</v>
       </c>
       <c r="I54" s="3">
-        <v>564940249</v>
+        <v>507965381</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="K54" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L54" s="3" t="s">
-        <v>411</v>
+        <v>395</v>
       </c>
       <c r="M54" s="1" t="s">
-        <v>412</v>
+        <v>396</v>
       </c>
     </row>
     <row r="55" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4854,38 +4854,38 @@
         <v>50</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="C55" s="3"/>
       <c r="D55" s="3" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="E55" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="H55" s="3">
-        <v>2401619040</v>
+        <v>2619028323</v>
       </c>
       <c r="I55" s="3">
-        <v>570393603</v>
+        <v>568794815</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="K55" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L55" s="3" t="s">
-        <v>406</v>
+        <v>395</v>
       </c>
       <c r="M55" s="1" t="s">
-        <v>405</v>
+        <v>394</v>
       </c>
     </row>
     <row r="56" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4894,36 +4894,38 @@
         <v>51</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="C56" s="3"/>
       <c r="D56" s="3" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="E56" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F56" s="3"/>
+      <c r="F56" s="3" t="s">
+        <v>227</v>
+      </c>
       <c r="G56" s="3" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="H56" s="3">
-        <v>2336749334</v>
+        <v>2578817971</v>
       </c>
       <c r="I56" s="3">
-        <v>507965381</v>
+        <v>568334710</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="K56" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L56" s="3" t="s">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="M56" s="1" t="s">
-        <v>407</v>
+        <v>397</v>
       </c>
     </row>
     <row r="57" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4932,38 +4934,38 @@
         <v>52</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="C57" s="3"/>
       <c r="D57" s="3" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="E57" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="H57" s="3">
-        <v>2619028323</v>
+        <v>2619028091</v>
       </c>
       <c r="I57" s="3">
-        <v>568794815</v>
+        <v>551621531</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="K57" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L57" s="3" t="s">
-        <v>406</v>
+        <v>395</v>
       </c>
       <c r="M57" s="1" t="s">
-        <v>405</v>
+        <v>394</v>
       </c>
     </row>
     <row r="58" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4972,38 +4974,38 @@
         <v>53</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="C58" s="3"/>
       <c r="D58" s="3" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="E58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F58" s="3" t="s">
-        <v>237</v>
+      <c r="F58" s="18">
+        <v>45880</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="H58" s="3">
-        <v>2578817971</v>
+        <v>2530062740</v>
       </c>
       <c r="I58" s="3">
-        <v>568334710</v>
+        <v>538325950</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>224</v>
+        <v>197</v>
       </c>
       <c r="K58" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L58" s="3" t="s">
-        <v>424</v>
+        <v>398</v>
       </c>
       <c r="M58" s="1" t="s">
-        <v>408</v>
+        <v>399</v>
       </c>
     </row>
     <row r="59" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5012,38 +5014,38 @@
         <v>54</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="C59" s="3"/>
       <c r="D59" s="3" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="E59" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="H59" s="3">
-        <v>2619028091</v>
+        <v>2591444696</v>
       </c>
       <c r="I59" s="3">
-        <v>551621531</v>
+        <v>541042125</v>
       </c>
       <c r="J59" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="K59" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L59" s="3" t="s">
-        <v>406</v>
+        <v>395</v>
       </c>
       <c r="M59" s="1" t="s">
-        <v>405</v>
+        <v>394</v>
       </c>
     </row>
     <row r="60" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5052,26 +5054,26 @@
         <v>55</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="C60" s="3"/>
       <c r="D60" s="3" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="E60" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F60" s="18">
-        <v>45880</v>
+      <c r="F60" s="3" t="s">
+        <v>238</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="H60" s="3">
-        <v>2530062740</v>
+        <v>2191037247</v>
       </c>
       <c r="I60" s="3">
-        <v>538325950</v>
+        <v>559227192</v>
       </c>
       <c r="J60" s="3" t="s">
         <v>207</v>
@@ -5080,10 +5082,10 @@
         <v>9</v>
       </c>
       <c r="L60" s="3" t="s">
-        <v>409</v>
+        <v>428</v>
       </c>
       <c r="M60" s="1" t="s">
-        <v>410</v>
+        <v>145</v>
       </c>
     </row>
     <row r="61" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5092,38 +5094,38 @@
         <v>56</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>225</v>
+        <v>402</v>
       </c>
       <c r="C61" s="3"/>
       <c r="D61" s="3" t="s">
         <v>241</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F61" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="G61" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="G61" s="3" t="s">
-        <v>244</v>
-      </c>
       <c r="H61" s="3">
-        <v>2591444696</v>
+        <v>2403517176</v>
       </c>
       <c r="I61" s="3">
-        <v>541042125</v>
+        <v>596807713</v>
       </c>
       <c r="J61" s="3" t="s">
-        <v>224</v>
+        <v>197</v>
       </c>
       <c r="K61" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L61" s="3" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="M61" s="1" t="s">
-        <v>405</v>
+        <v>396</v>
       </c>
     </row>
     <row r="62" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5132,38 +5134,38 @@
         <v>57</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>246</v>
+        <v>402</v>
       </c>
       <c r="C62" s="3"/>
       <c r="D62" s="3" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="H62" s="3">
-        <v>2191037247</v>
-      </c>
-      <c r="I62" s="3">
-        <v>559227192</v>
+        <v>2456946371</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>246</v>
       </c>
       <c r="J62" s="3" t="s">
-        <v>217</v>
+        <v>197</v>
       </c>
       <c r="K62" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L62" s="3" t="s">
-        <v>439</v>
+        <v>395</v>
       </c>
       <c r="M62" s="1" t="s">
-        <v>154</v>
+        <v>394</v>
       </c>
     </row>
     <row r="63" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5172,38 +5174,38 @@
         <v>58</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>413</v>
+        <v>402</v>
       </c>
       <c r="C63" s="3"/>
       <c r="D63" s="3" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="E63" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F63" s="3" t="s">
-        <v>252</v>
+      <c r="F63" s="18">
+        <v>45912</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="H63" s="3">
-        <v>2403517176</v>
+        <v>2554390837</v>
       </c>
       <c r="I63" s="3">
-        <v>596807713</v>
+        <v>597862998</v>
       </c>
       <c r="J63" s="3" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="K63" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L63" s="3" t="s">
-        <v>414</v>
+        <v>425</v>
       </c>
       <c r="M63" s="1" t="s">
-        <v>407</v>
+        <v>426</v>
       </c>
     </row>
     <row r="64" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5212,38 +5214,38 @@
         <v>59</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>413</v>
+        <v>402</v>
       </c>
       <c r="C64" s="3"/>
       <c r="D64" s="3" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="E64" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F64" s="3" t="s">
-        <v>254</v>
+      <c r="F64" s="18">
+        <v>45785</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="H64" s="3">
-        <v>2456946371</v>
-      </c>
-      <c r="I64" s="3" t="s">
-        <v>256</v>
+        <v>2595525672</v>
+      </c>
+      <c r="I64" s="3">
+        <v>573185662</v>
       </c>
       <c r="J64" s="3" t="s">
-        <v>207</v>
+        <v>240</v>
       </c>
       <c r="K64" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L64" s="3" t="s">
-        <v>406</v>
+        <v>395</v>
       </c>
       <c r="M64" s="1" t="s">
-        <v>405</v>
+        <v>394</v>
       </c>
     </row>
     <row r="65" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5252,38 +5254,38 @@
         <v>60</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>413</v>
+        <v>402</v>
       </c>
       <c r="C65" s="3"/>
       <c r="D65" s="3" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="E65" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F65" s="18">
-        <v>45912</v>
+      <c r="F65" s="3" t="s">
+        <v>251</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="H65" s="3">
-        <v>2554390837</v>
+        <v>2619028661</v>
       </c>
       <c r="I65" s="3">
-        <v>597862998</v>
+        <v>553458321</v>
       </c>
       <c r="J65" s="3" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="K65" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L65" s="3" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
       <c r="M65" s="1" t="s">
-        <v>437</v>
+        <v>429</v>
       </c>
     </row>
     <row r="66" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5292,38 +5294,38 @@
         <v>61</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>413</v>
+        <v>402</v>
       </c>
       <c r="C66" s="3"/>
       <c r="D66" s="3" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="E66" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F66" s="18">
-        <v>45785</v>
+      <c r="F66" s="3" t="s">
+        <v>229</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="H66" s="3">
-        <v>2595525672</v>
+        <v>2613784996</v>
       </c>
       <c r="I66" s="3">
-        <v>573185662</v>
+        <v>509924171</v>
       </c>
       <c r="J66" s="3" t="s">
-        <v>250</v>
+        <v>197</v>
       </c>
       <c r="K66" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L66" s="3" t="s">
-        <v>406</v>
+        <v>395</v>
       </c>
       <c r="M66" s="1" t="s">
-        <v>405</v>
+        <v>394</v>
       </c>
     </row>
     <row r="67" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5332,26 +5334,24 @@
         <v>62</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>413</v>
+        <v>402</v>
       </c>
       <c r="C67" s="3"/>
       <c r="D67" s="3" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="E67" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F67" s="3" t="s">
-        <v>261</v>
-      </c>
+      <c r="F67" s="3"/>
       <c r="G67" s="3" t="s">
-        <v>262</v>
+        <v>418</v>
       </c>
       <c r="H67" s="3">
-        <v>2619028661</v>
+        <v>2405112414</v>
       </c>
       <c r="I67" s="3">
-        <v>553458321</v>
+        <v>581782627</v>
       </c>
       <c r="J67" s="3" t="s">
         <v>207</v>
@@ -5360,10 +5360,10 @@
         <v>9</v>
       </c>
       <c r="L67" s="3" t="s">
-        <v>441</v>
+        <v>417</v>
       </c>
       <c r="M67" s="1" t="s">
-        <v>440</v>
+        <v>145</v>
       </c>
     </row>
     <row r="68" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5372,2864 +5372,2876 @@
         <v>63</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>413</v>
+        <v>402</v>
       </c>
       <c r="C68" s="3"/>
       <c r="D68" s="3" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="E68" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>239</v>
+        <v>255</v>
       </c>
       <c r="G68" s="3" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="H68" s="3">
-        <v>2613784996</v>
+        <v>2568894667</v>
       </c>
       <c r="I68" s="3">
-        <v>509924171</v>
+        <v>564785053</v>
       </c>
       <c r="J68" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="K68" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L68" s="3" t="s">
-        <v>406</v>
+        <v>395</v>
       </c>
       <c r="M68" s="1" t="s">
-        <v>405</v>
+        <v>394</v>
       </c>
     </row>
     <row r="69" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="A69:A78" si="24">A68+1</f>
         <v>64</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>413</v>
+        <v>402</v>
       </c>
       <c r="C69" s="3"/>
       <c r="D69" s="3" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="E69" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F69" s="3"/>
+      <c r="F69" s="18">
+        <v>45813</v>
+      </c>
       <c r="G69" s="3" t="s">
-        <v>429</v>
+        <v>258</v>
       </c>
       <c r="H69" s="3">
-        <v>1</v>
+        <v>2572129837</v>
       </c>
       <c r="I69" s="3">
-        <v>581782627</v>
+        <v>581726525</v>
       </c>
       <c r="J69" s="3" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="K69" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L69" s="3" t="s">
-        <v>428</v>
+        <v>437</v>
       </c>
       <c r="M69" s="1" t="s">
-        <v>154</v>
+        <v>394</v>
       </c>
     </row>
     <row r="70" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="24"/>
         <v>65</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>413</v>
+        <v>402</v>
       </c>
       <c r="C70" s="3"/>
       <c r="D70" s="3" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="E70" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="G70" s="3" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="H70" s="3">
-        <v>2568894667</v>
+        <v>2619027283</v>
       </c>
       <c r="I70" s="3">
-        <v>564785053</v>
+        <v>551072957</v>
       </c>
       <c r="J70" s="3" t="s">
-        <v>224</v>
+        <v>197</v>
       </c>
       <c r="K70" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L70" s="3" t="s">
-        <v>406</v>
+        <v>395</v>
       </c>
       <c r="M70" s="1" t="s">
-        <v>405</v>
+        <v>394</v>
       </c>
     </row>
     <row r="71" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
-        <f t="shared" ref="A71:A80" si="1">A70+1</f>
+        <f t="shared" si="24"/>
         <v>66</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>413</v>
+        <v>402</v>
       </c>
       <c r="C71" s="3"/>
       <c r="D71" s="3" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="E71" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F71" s="18">
-        <v>45813</v>
+      <c r="F71" s="3" t="s">
+        <v>262</v>
       </c>
       <c r="G71" s="3" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="H71" s="3">
-        <v>2572129837</v>
+        <v>2610862597</v>
       </c>
       <c r="I71" s="3">
-        <v>581726525</v>
+        <v>506802815</v>
       </c>
       <c r="J71" s="3" t="s">
-        <v>217</v>
+        <v>240</v>
       </c>
       <c r="K71" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L71" s="3" t="s">
-        <v>448</v>
+        <v>431</v>
       </c>
       <c r="M71" s="1" t="s">
-        <v>405</v>
+        <v>432</v>
       </c>
     </row>
     <row r="72" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="24"/>
         <v>67</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>413</v>
+        <v>402</v>
       </c>
       <c r="C72" s="3"/>
       <c r="D72" s="3" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="G72" s="3" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="H72" s="3">
-        <v>2619027283</v>
+        <v>2619028562</v>
       </c>
       <c r="I72" s="3">
-        <v>1</v>
+        <v>509723603</v>
       </c>
       <c r="J72" s="3" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="K72" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L72" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="M72" s="1" t="s">
-        <v>405</v>
+        <v>190</v>
       </c>
     </row>
     <row r="73" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="24"/>
         <v>68</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>413</v>
+        <v>402</v>
       </c>
       <c r="C73" s="3"/>
       <c r="D73" s="3" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F73" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="G73" s="3" t="s">
-        <v>273</v>
+        <v>267</v>
+      </c>
+      <c r="G73" s="26" t="s">
+        <v>549</v>
       </c>
       <c r="H73" s="3">
-        <v>2610862597</v>
+        <v>2488877537</v>
       </c>
       <c r="I73" s="3">
-        <v>506802815</v>
+        <v>536382782</v>
       </c>
       <c r="J73" s="3" t="s">
-        <v>250</v>
+        <v>197</v>
       </c>
       <c r="K73" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L73" s="3" t="s">
-        <v>442</v>
+        <v>395</v>
       </c>
       <c r="M73" s="1" t="s">
-        <v>443</v>
+        <v>394</v>
       </c>
     </row>
     <row r="74" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="24"/>
         <v>69</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>413</v>
+        <v>268</v>
       </c>
       <c r="C74" s="3"/>
       <c r="D74" s="3" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="E74" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F74" s="3" t="s">
-        <v>275</v>
+      <c r="F74" s="18">
+        <v>45907</v>
       </c>
       <c r="G74" s="3" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="H74" s="3">
-        <v>2619028562</v>
+        <v>2542416488</v>
       </c>
       <c r="I74" s="3">
-        <v>509723603</v>
+        <v>550093981</v>
       </c>
       <c r="J74" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="K74" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L74" s="3" t="s">
-        <v>423</v>
+        <v>387</v>
       </c>
       <c r="M74" s="1" t="s">
-        <v>200</v>
+        <v>474</v>
       </c>
     </row>
     <row r="75" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="24"/>
         <v>70</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>413</v>
+        <v>268</v>
       </c>
       <c r="C75" s="3"/>
       <c r="D75" s="3" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="E75" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F75" s="3" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="G75" s="3" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="H75" s="3">
-        <v>2528374557</v>
+        <v>2411296102</v>
       </c>
       <c r="I75" s="3">
-        <v>1</v>
+        <v>580931391</v>
       </c>
       <c r="J75" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="K75" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L75" s="3" t="s">
-        <v>406</v>
+        <v>387</v>
       </c>
       <c r="M75" s="1" t="s">
-        <v>405</v>
+        <v>474</v>
       </c>
     </row>
     <row r="76" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="24"/>
         <v>71</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>279</v>
+        <v>268</v>
       </c>
       <c r="C76" s="3"/>
       <c r="D76" s="3" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="E76" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F76" s="18">
-        <v>45907</v>
+      <c r="F76" s="3" t="s">
+        <v>274</v>
       </c>
       <c r="G76" s="3" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="H76" s="3">
-        <v>2542416488</v>
+        <v>2456942891</v>
       </c>
       <c r="I76" s="3">
-        <v>550093981</v>
+        <v>599390362</v>
       </c>
       <c r="J76" s="3" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="K76" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L76" s="3" t="s">
-        <v>398</v>
+        <v>387</v>
       </c>
       <c r="M76" s="1" t="s">
-        <v>485</v>
+        <v>474</v>
       </c>
     </row>
     <row r="77" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="24"/>
         <v>72</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>279</v>
+        <v>268</v>
       </c>
       <c r="C77" s="3"/>
       <c r="D77" s="3" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="E77" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F77" s="3" t="s">
-        <v>282</v>
+        <v>220</v>
       </c>
       <c r="G77" s="3" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="H77" s="3">
-        <v>2411296102</v>
+        <v>2532576192</v>
       </c>
       <c r="I77" s="3">
-        <v>580931391</v>
+        <v>583260857</v>
       </c>
       <c r="J77" s="3" t="s">
-        <v>224</v>
+        <v>197</v>
       </c>
       <c r="K77" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L77" s="3" t="s">
-        <v>398</v>
+        <v>387</v>
       </c>
       <c r="M77" s="1" t="s">
-        <v>485</v>
+        <v>474</v>
       </c>
     </row>
     <row r="78" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="24"/>
         <v>73</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>279</v>
+        <v>268</v>
       </c>
       <c r="C78" s="3"/>
       <c r="D78" s="3" t="s">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="E78" s="3" t="s">
         <v>5</v>
       </c>
       <c r="F78" s="3" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="G78" s="3" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="H78" s="3">
-        <v>2456942891</v>
+        <v>2586692531</v>
       </c>
       <c r="I78" s="3">
-        <v>599390362</v>
+        <v>502150791</v>
       </c>
       <c r="J78" s="3" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="K78" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L78" s="3" t="s">
-        <v>398</v>
+        <v>387</v>
       </c>
       <c r="M78" s="1" t="s">
-        <v>485</v>
+        <v>474</v>
       </c>
     </row>
     <row r="79" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="A79:A117" si="25">A78+1</f>
         <v>74</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>279</v>
+        <v>268</v>
       </c>
       <c r="C79" s="3"/>
       <c r="D79" s="3" t="s">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="E79" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F79" s="3" t="s">
-        <v>230</v>
+      <c r="F79" s="18">
+        <v>45842</v>
       </c>
       <c r="G79" s="3" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="H79" s="3">
-        <v>2532576192</v>
+        <v>2527665414</v>
       </c>
       <c r="I79" s="3">
-        <v>583260857</v>
+        <v>543216803</v>
       </c>
       <c r="J79" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="K79" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L79" s="3" t="s">
-        <v>398</v>
+        <v>387</v>
       </c>
       <c r="M79" s="1" t="s">
-        <v>485</v>
+        <v>474</v>
       </c>
     </row>
     <row r="80" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="25"/>
         <v>75</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>279</v>
+        <v>268</v>
       </c>
       <c r="C80" s="3"/>
       <c r="D80" s="3" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="E80" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F80" s="3" t="s">
-        <v>289</v>
+      <c r="F80" s="18">
+        <v>45758</v>
       </c>
       <c r="G80" s="3" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="H80" s="3">
-        <v>2586692531</v>
+        <v>2549319693</v>
       </c>
       <c r="I80" s="3">
-        <v>502150791</v>
+        <v>572534118</v>
       </c>
       <c r="J80" s="3" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="K80" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L80" s="3" t="s">
-        <v>398</v>
+        <v>387</v>
       </c>
       <c r="M80" s="1" t="s">
-        <v>485</v>
+        <v>474</v>
       </c>
     </row>
     <row r="81" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
-        <f t="shared" ref="A81:A119" si="2">A80+1</f>
+        <f t="shared" si="25"/>
         <v>76</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>279</v>
+        <v>268</v>
       </c>
       <c r="C81" s="3"/>
       <c r="D81" s="3" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="E81" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F81" s="18">
-        <v>45842</v>
+      <c r="F81" s="3" t="s">
+        <v>283</v>
       </c>
       <c r="G81" s="3" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="H81" s="3">
-        <v>2527665414</v>
+        <v>2619815406</v>
       </c>
       <c r="I81" s="3">
-        <v>543216803</v>
+        <v>530268978</v>
       </c>
       <c r="J81" s="3" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="K81" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L81" s="3" t="s">
-        <v>398</v>
+        <v>387</v>
       </c>
       <c r="M81" s="1" t="s">
-        <v>485</v>
+        <v>474</v>
       </c>
     </row>
     <row r="82" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="25"/>
         <v>77</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>279</v>
+        <v>268</v>
       </c>
       <c r="C82" s="3"/>
       <c r="D82" s="3" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="E82" s="3" t="s">
         <v>5</v>
       </c>
       <c r="F82" s="18">
-        <v>45758</v>
+        <v>45907</v>
       </c>
       <c r="G82" s="3" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="H82" s="3">
-        <v>2549319693</v>
+        <v>2565023492</v>
       </c>
       <c r="I82" s="3">
-        <v>572534118</v>
+        <v>509133276</v>
       </c>
       <c r="J82" s="3" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="K82" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L82" s="3" t="s">
-        <v>398</v>
+        <v>387</v>
       </c>
       <c r="M82" s="1" t="s">
-        <v>485</v>
+        <v>474</v>
       </c>
     </row>
     <row r="83" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="25"/>
         <v>78</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>279</v>
+        <v>268</v>
       </c>
       <c r="C83" s="3"/>
       <c r="D83" s="3" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="E83" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F83" s="3" t="s">
-        <v>294</v>
+      <c r="F83" s="18">
+        <v>45727</v>
       </c>
       <c r="G83" s="3" t="s">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="H83" s="3">
-        <v>2619815406</v>
+        <v>2509152142</v>
       </c>
       <c r="I83" s="3">
-        <v>530268978</v>
+        <v>556988467</v>
       </c>
       <c r="J83" s="3" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="K83" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L83" s="3" t="s">
-        <v>398</v>
+        <v>387</v>
       </c>
       <c r="M83" s="1" t="s">
-        <v>485</v>
+        <v>474</v>
       </c>
     </row>
     <row r="84" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="25"/>
         <v>79</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>279</v>
+        <v>268</v>
       </c>
       <c r="C84" s="3"/>
       <c r="D84" s="3" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="E84" s="3" t="s">
         <v>5</v>
       </c>
       <c r="F84" s="18">
-        <v>45907</v>
+        <v>45727</v>
       </c>
       <c r="G84" s="3" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="H84" s="3">
-        <v>2565023492</v>
+        <v>2528735539</v>
       </c>
       <c r="I84" s="3">
-        <v>509133276</v>
+        <v>532514819</v>
       </c>
       <c r="J84" s="3" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="K84" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L84" s="3" t="s">
-        <v>398</v>
+        <v>387</v>
       </c>
       <c r="M84" s="1" t="s">
-        <v>485</v>
+        <v>474</v>
       </c>
     </row>
     <row r="85" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="25"/>
         <v>80</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>279</v>
+        <v>268</v>
       </c>
       <c r="C85" s="3"/>
       <c r="D85" s="3" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="E85" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F85" s="18">
-        <v>45727</v>
+      <c r="F85" s="3" t="s">
+        <v>220</v>
       </c>
       <c r="G85" s="3" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="H85" s="3">
-        <v>2509152142</v>
+        <v>2515420509</v>
       </c>
       <c r="I85" s="3">
-        <v>556988467</v>
+        <v>547860195</v>
       </c>
       <c r="J85" s="3" t="s">
-        <v>224</v>
+        <v>197</v>
       </c>
       <c r="K85" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L85" s="3" t="s">
-        <v>398</v>
+        <v>387</v>
       </c>
       <c r="M85" s="1" t="s">
-        <v>485</v>
+        <v>474</v>
       </c>
     </row>
     <row r="86" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="25"/>
         <v>81</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>279</v>
+        <v>268</v>
       </c>
       <c r="C86" s="3"/>
       <c r="D86" s="3" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="E86" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F86" s="18">
-        <v>45727</v>
+      <c r="F86" s="3" t="s">
+        <v>292</v>
       </c>
       <c r="G86" s="3" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="H86" s="3">
-        <v>2528735539</v>
+        <v>2550655894</v>
       </c>
       <c r="I86" s="3">
-        <v>532514819</v>
+        <v>575987366</v>
       </c>
       <c r="J86" s="3" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="K86" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L86" s="3" t="s">
-        <v>398</v>
+        <v>387</v>
       </c>
       <c r="M86" s="1" t="s">
-        <v>485</v>
+        <v>474</v>
       </c>
     </row>
     <row r="87" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="25"/>
         <v>82</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>279</v>
+        <v>268</v>
       </c>
       <c r="C87" s="3"/>
       <c r="D87" s="3" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="E87" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F87" s="3" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="G87" s="3" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="H87" s="3">
-        <v>2515420509</v>
+        <v>2530062880</v>
       </c>
       <c r="I87" s="3">
-        <v>547860195</v>
+        <v>558521436</v>
       </c>
       <c r="J87" s="3" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="K87" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L87" s="3" t="s">
-        <v>398</v>
+        <v>387</v>
       </c>
       <c r="M87" s="1" t="s">
-        <v>485</v>
+        <v>474</v>
       </c>
     </row>
     <row r="88" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="25"/>
         <v>83</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>279</v>
+        <v>295</v>
       </c>
       <c r="C88" s="3"/>
       <c r="D88" s="3" t="s">
-        <v>302</v>
+        <v>406</v>
       </c>
       <c r="E88" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F88" s="3" t="s">
-        <v>303</v>
+      <c r="F88" s="18">
+        <v>45788</v>
       </c>
       <c r="G88" s="3" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="H88" s="3">
-        <v>2550655894</v>
+        <v>2524755531</v>
       </c>
       <c r="I88" s="3">
-        <v>575987366</v>
+        <v>559318019</v>
       </c>
       <c r="J88" s="3" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="K88" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L88" s="3" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="M88" s="1" t="s">
-        <v>485</v>
+        <v>405</v>
       </c>
     </row>
     <row r="89" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="25"/>
         <v>84</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>279</v>
+        <v>295</v>
       </c>
       <c r="C89" s="3"/>
       <c r="D89" s="3" t="s">
-        <v>302</v>
+        <v>406</v>
       </c>
       <c r="E89" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F89" s="3" t="s">
-        <v>230</v>
+      <c r="F89" s="18">
+        <v>45879</v>
       </c>
       <c r="G89" s="3" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="H89" s="3">
-        <v>2530062880</v>
+        <v>2610325934</v>
       </c>
       <c r="I89" s="3">
-        <v>558521436</v>
+        <v>546337608</v>
       </c>
       <c r="J89" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="K89" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L89" s="3" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="M89" s="1" t="s">
-        <v>485</v>
+        <v>394</v>
       </c>
     </row>
     <row r="90" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="25"/>
         <v>85</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>306</v>
+        <v>295</v>
       </c>
       <c r="C90" s="3"/>
       <c r="D90" s="3" t="s">
-        <v>417</v>
+        <v>298</v>
       </c>
       <c r="E90" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F90" s="18">
-        <v>45788</v>
+      <c r="F90" s="3" t="s">
+        <v>262</v>
       </c>
       <c r="G90" s="3" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="H90" s="3">
-        <v>2524755531</v>
+        <v>2575098062</v>
       </c>
       <c r="I90" s="3">
-        <v>559318019</v>
+        <v>547884897</v>
       </c>
       <c r="J90" s="3" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="K90" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L90" s="3" t="s">
-        <v>415</v>
+        <v>392</v>
       </c>
       <c r="M90" s="1" t="s">
-        <v>416</v>
+        <v>393</v>
       </c>
     </row>
     <row r="91" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="25"/>
         <v>86</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>306</v>
+        <v>295</v>
       </c>
       <c r="C91" s="3"/>
       <c r="D91" s="3" t="s">
-        <v>417</v>
+        <v>298</v>
       </c>
       <c r="E91" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F91" s="18">
-        <v>45879</v>
+        <v>45725</v>
       </c>
       <c r="G91" s="3" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="H91" s="3">
-        <v>2610325934</v>
+        <v>2532575913</v>
       </c>
       <c r="I91" s="3">
-        <v>546337608</v>
+        <v>553954783</v>
       </c>
       <c r="J91" s="3" t="s">
-        <v>224</v>
+        <v>197</v>
       </c>
       <c r="K91" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L91" s="3" t="s">
-        <v>406</v>
+        <v>392</v>
       </c>
       <c r="M91" s="1" t="s">
-        <v>405</v>
+        <v>394</v>
       </c>
     </row>
     <row r="92" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="25"/>
         <v>87</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>306</v>
+        <v>295</v>
       </c>
       <c r="C92" s="3"/>
       <c r="D92" s="3" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="E92" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F92" s="3" t="s">
-        <v>272</v>
+      <c r="F92" s="18">
+        <v>45758</v>
       </c>
       <c r="G92" s="3" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="H92" s="3">
-        <v>2575098062</v>
+        <v>2530061908</v>
       </c>
       <c r="I92" s="3">
-        <v>547884897</v>
+        <v>582818513</v>
       </c>
       <c r="J92" s="3" t="s">
-        <v>224</v>
+        <v>197</v>
       </c>
       <c r="K92" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L92" s="3" t="s">
-        <v>403</v>
+        <v>435</v>
       </c>
       <c r="M92" s="1" t="s">
-        <v>404</v>
+        <v>145</v>
       </c>
     </row>
     <row r="93" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="25"/>
         <v>88</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>306</v>
+        <v>295</v>
       </c>
       <c r="C93" s="3"/>
       <c r="D93" s="3" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="E93" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F93" s="18">
-        <v>45725</v>
+      <c r="F93" s="3" t="s">
+        <v>303</v>
       </c>
       <c r="G93" s="3" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="H93" s="3">
-        <v>2532575913</v>
+        <v>2522755582</v>
       </c>
       <c r="I93" s="3">
-        <v>553954783</v>
+        <v>571430053</v>
       </c>
       <c r="J93" s="3" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="K93" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L93" s="3" t="s">
-        <v>403</v>
+        <v>436</v>
       </c>
       <c r="M93" s="1" t="s">
-        <v>405</v>
+        <v>394</v>
       </c>
     </row>
     <row r="94" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="25"/>
         <v>89</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C94" s="3"/>
       <c r="D94" s="3" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="E94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F94" s="18">
-        <v>45758</v>
+      <c r="F94" s="3" t="s">
+        <v>278</v>
       </c>
       <c r="G94" s="3" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="H94" s="3">
-        <v>2530061908</v>
+        <v>2391588452</v>
       </c>
       <c r="I94" s="3">
-        <v>582818513</v>
+        <v>597887245</v>
       </c>
       <c r="J94" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="K94" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L94" s="3" t="s">
-        <v>446</v>
+        <v>392</v>
       </c>
       <c r="M94" s="1" t="s">
-        <v>154</v>
+        <v>393</v>
       </c>
     </row>
     <row r="95" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="25"/>
         <v>90</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C95" s="3"/>
       <c r="D95" s="3" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="E95" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F95" s="3" t="s">
-        <v>314</v>
+      <c r="F95" s="18">
+        <v>45842</v>
       </c>
       <c r="G95" s="3" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="H95" s="3">
-        <v>2522755582</v>
+        <v>2597984943</v>
       </c>
       <c r="I95" s="3">
-        <v>571430053</v>
+        <v>548785540</v>
       </c>
       <c r="J95" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="K95" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L95" s="3" t="s">
-        <v>447</v>
+        <v>392</v>
       </c>
       <c r="M95" s="1" t="s">
-        <v>405</v>
+        <v>393</v>
       </c>
     </row>
     <row r="96" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="25"/>
         <v>91</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>316</v>
+        <v>305</v>
       </c>
       <c r="C96" s="3"/>
       <c r="D96" s="3" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="E96" s="3" t="s">
         <v>5</v>
       </c>
       <c r="F96" s="3" t="s">
-        <v>289</v>
+        <v>310</v>
       </c>
       <c r="G96" s="3" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="H96" s="3">
-        <v>2391588452</v>
+        <v>2398589008</v>
       </c>
       <c r="I96" s="3">
-        <v>597887245</v>
+        <v>592532800</v>
       </c>
       <c r="J96" s="3" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="K96" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L96" s="3" t="s">
-        <v>403</v>
+        <v>391</v>
       </c>
       <c r="M96" s="1" t="s">
-        <v>404</v>
+        <v>145</v>
       </c>
     </row>
     <row r="97" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="25"/>
         <v>92</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>316</v>
+        <v>305</v>
       </c>
       <c r="C97" s="3"/>
       <c r="D97" s="3" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="E97" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F97" s="18">
-        <v>45842</v>
+      <c r="F97" s="3" t="s">
+        <v>312</v>
       </c>
       <c r="G97" s="3" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="H97" s="3">
-        <v>2597984943</v>
+        <v>2524755762</v>
       </c>
       <c r="I97" s="3">
-        <v>548785540</v>
+        <v>507959127</v>
       </c>
       <c r="J97" s="3" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="K97" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L97" s="3" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
       <c r="M97" s="1" t="s">
-        <v>404</v>
+        <v>393</v>
       </c>
     </row>
     <row r="98" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="25"/>
         <v>93</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>316</v>
+        <v>305</v>
       </c>
       <c r="C98" s="3"/>
       <c r="D98" s="3" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="E98" s="3" t="s">
         <v>5</v>
       </c>
       <c r="F98" s="3" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="G98" s="3" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="H98" s="3">
-        <v>2398589008</v>
+        <v>2489066601</v>
       </c>
       <c r="I98" s="3">
-        <v>592532800</v>
+        <v>580311048</v>
       </c>
       <c r="J98" s="3" t="s">
-        <v>224</v>
+        <v>197</v>
       </c>
       <c r="K98" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L98" s="3" t="s">
-        <v>402</v>
+        <v>392</v>
       </c>
       <c r="M98" s="1" t="s">
-        <v>154</v>
+        <v>393</v>
       </c>
     </row>
     <row r="99" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="25"/>
         <v>94</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>316</v>
+        <v>305</v>
       </c>
       <c r="C99" s="3"/>
       <c r="D99" s="3" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F99" s="3" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="G99" s="3" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="H99" s="3">
-        <v>2524755762</v>
+        <v>2528735109</v>
       </c>
       <c r="I99" s="3">
-        <v>507959127</v>
+        <v>555875763</v>
       </c>
       <c r="J99" s="3" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="K99" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L99" s="3" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
       <c r="M99" s="1" t="s">
-        <v>404</v>
+        <v>393</v>
       </c>
     </row>
     <row r="100" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="25"/>
         <v>95</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>316</v>
+        <v>305</v>
       </c>
       <c r="C100" s="3"/>
       <c r="D100" s="3" t="s">
-        <v>325</v>
+        <v>317</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F100" s="3" t="s">
-        <v>326</v>
+        <v>10</v>
+      </c>
+      <c r="F100" s="18">
+        <v>45758</v>
       </c>
       <c r="G100" s="3" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="H100" s="3">
-        <v>2489066601</v>
+        <v>2541103426</v>
       </c>
       <c r="I100" s="3">
-        <v>580311048</v>
+        <v>502662580</v>
       </c>
       <c r="J100" s="3" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="K100" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L100" s="3" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
       <c r="M100" s="1" t="s">
-        <v>404</v>
+        <v>394</v>
       </c>
     </row>
     <row r="101" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="25"/>
         <v>96</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>316</v>
+        <v>305</v>
       </c>
       <c r="C101" s="3"/>
       <c r="D101" s="3" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F101" s="3" t="s">
-        <v>329</v>
+        <v>238</v>
       </c>
       <c r="G101" s="3" t="s">
-        <v>330</v>
+        <v>322</v>
       </c>
       <c r="H101" s="3">
-        <v>2528735109</v>
+        <v>2522755673</v>
       </c>
       <c r="I101" s="3">
-        <v>555875763</v>
+        <v>573007369</v>
       </c>
       <c r="J101" s="3" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="K101" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L101" s="3" t="s">
-        <v>403</v>
+        <v>395</v>
       </c>
       <c r="M101" s="1" t="s">
-        <v>404</v>
+        <v>394</v>
       </c>
     </row>
     <row r="102" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="25"/>
         <v>97</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="C102" s="3"/>
       <c r="D102" s="3" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F102" s="18">
-        <v>45758</v>
+        <v>45906</v>
       </c>
       <c r="G102" s="3" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="H102" s="3">
-        <v>2541103426</v>
+        <v>2601128438</v>
       </c>
       <c r="I102" s="3">
-        <v>502662580</v>
+        <v>501583202</v>
       </c>
       <c r="J102" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="K102" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L102" s="3" t="s">
-        <v>403</v>
+        <v>390</v>
       </c>
       <c r="M102" s="1" t="s">
-        <v>405</v>
+        <v>389</v>
       </c>
     </row>
     <row r="103" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="25"/>
         <v>98</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="C103" s="3"/>
       <c r="D103" s="3" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="E103" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F103" s="3" t="s">
-        <v>248</v>
+      <c r="F103" s="18">
+        <v>46023</v>
       </c>
       <c r="G103" s="3" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="H103" s="3">
-        <v>2522755673</v>
+        <v>2528096148</v>
       </c>
       <c r="I103" s="3">
-        <v>573007369</v>
+        <v>551809623</v>
       </c>
       <c r="J103" s="3" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="K103" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L103" s="3" t="s">
-        <v>406</v>
+        <v>390</v>
       </c>
       <c r="M103" s="1" t="s">
-        <v>405</v>
+        <v>389</v>
       </c>
     </row>
     <row r="104" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="25"/>
         <v>99</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>334</v>
+        <v>323</v>
       </c>
       <c r="C104" s="3"/>
       <c r="D104" s="3" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="E104" s="3" t="s">
         <v>5</v>
       </c>
       <c r="F104" s="18">
-        <v>45906</v>
+        <v>45992</v>
       </c>
       <c r="G104" s="3" t="s">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="H104" s="3">
-        <v>2601128438</v>
+        <v>2489338703</v>
       </c>
       <c r="I104" s="3">
-        <v>501583202</v>
+        <v>572988291</v>
       </c>
       <c r="J104" s="3" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="K104" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L104" s="3" t="s">
-        <v>401</v>
+        <v>390</v>
       </c>
       <c r="M104" s="1" t="s">
-        <v>400</v>
+        <v>389</v>
       </c>
     </row>
     <row r="105" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="25"/>
         <v>100</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>334</v>
+        <v>323</v>
       </c>
       <c r="C105" s="3"/>
       <c r="D105" s="3" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="E105" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F105" s="18">
-        <v>46023</v>
+        <v>45937</v>
       </c>
       <c r="G105" s="3" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="H105" s="3">
-        <v>2528096148</v>
+        <v>2597473368</v>
       </c>
       <c r="I105" s="3">
-        <v>551809623</v>
+        <v>538958654</v>
       </c>
       <c r="J105" s="3" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="K105" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L105" s="3" t="s">
-        <v>401</v>
+        <v>390</v>
       </c>
       <c r="M105" s="1" t="s">
-        <v>400</v>
+        <v>389</v>
       </c>
     </row>
     <row r="106" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="25"/>
         <v>101</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>334</v>
+        <v>323</v>
       </c>
       <c r="C106" s="3"/>
       <c r="D106" s="3" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="E106" s="3" t="s">
         <v>5</v>
       </c>
       <c r="F106" s="18">
-        <v>45992</v>
+        <v>45758</v>
       </c>
       <c r="G106" s="3" t="s">
-        <v>339</v>
+        <v>331</v>
       </c>
       <c r="H106" s="3">
-        <v>2489338703</v>
+        <v>2618349555</v>
       </c>
       <c r="I106" s="3">
-        <v>572988291</v>
+        <v>537625501</v>
       </c>
       <c r="J106" s="3" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="K106" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L106" s="3" t="s">
-        <v>401</v>
+        <v>390</v>
       </c>
       <c r="M106" s="1" t="s">
-        <v>400</v>
+        <v>389</v>
       </c>
     </row>
     <row r="107" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="25"/>
         <v>102</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>334</v>
+        <v>323</v>
       </c>
       <c r="C107" s="3"/>
       <c r="D107" s="3" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="E107" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F107" s="18">
-        <v>45937</v>
+        <v>45638</v>
       </c>
       <c r="G107" s="3" t="s">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="H107" s="3">
-        <v>2597473368</v>
+        <v>2530063110</v>
       </c>
       <c r="I107" s="3">
-        <v>538958654</v>
+        <v>558523106</v>
       </c>
       <c r="J107" s="3" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="K107" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L107" s="3" t="s">
-        <v>401</v>
+        <v>390</v>
       </c>
       <c r="M107" s="1" t="s">
-        <v>400</v>
+        <v>389</v>
       </c>
     </row>
     <row r="108" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="25"/>
         <v>103</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>334</v>
+        <v>323</v>
       </c>
       <c r="C108" s="3"/>
       <c r="D108" s="3" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="E108" s="3" t="s">
         <v>5</v>
       </c>
       <c r="F108" s="18">
-        <v>45758</v>
+        <v>45992</v>
       </c>
       <c r="G108" s="3" t="s">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="H108" s="3">
-        <v>2618349555</v>
+        <v>2419547381</v>
       </c>
       <c r="I108" s="3">
-        <v>537625501</v>
+        <v>599307374</v>
       </c>
       <c r="J108" s="3" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="K108" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L108" s="3" t="s">
-        <v>401</v>
+        <v>390</v>
       </c>
       <c r="M108" s="1" t="s">
-        <v>400</v>
+        <v>389</v>
       </c>
     </row>
     <row r="109" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="25"/>
         <v>104</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>334</v>
+        <v>323</v>
       </c>
       <c r="C109" s="3"/>
       <c r="D109" s="3" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="E109" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F109" s="18">
-        <v>45638</v>
+      <c r="F109" s="3" t="s">
+        <v>292</v>
       </c>
       <c r="G109" s="3" t="s">
-        <v>343</v>
+        <v>335</v>
       </c>
       <c r="H109" s="3">
-        <v>2530063110</v>
+        <v>2528098284</v>
       </c>
       <c r="I109" s="3">
-        <v>558523106</v>
+        <v>572004402</v>
       </c>
       <c r="J109" s="3" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="K109" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L109" s="3" t="s">
-        <v>401</v>
+        <v>390</v>
       </c>
       <c r="M109" s="1" t="s">
-        <v>400</v>
+        <v>389</v>
       </c>
     </row>
     <row r="110" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="25"/>
         <v>105</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>334</v>
+        <v>323</v>
       </c>
       <c r="C110" s="3"/>
       <c r="D110" s="3" t="s">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="E110" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F110" s="18">
-        <v>45992</v>
+      <c r="F110" s="3" t="s">
+        <v>220</v>
       </c>
       <c r="G110" s="3" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="H110" s="3">
-        <v>2419547381</v>
+        <v>2536636620</v>
       </c>
       <c r="I110" s="3">
-        <v>599307374</v>
+        <v>549284079</v>
       </c>
       <c r="J110" s="3" t="s">
-        <v>224</v>
+        <v>197</v>
       </c>
       <c r="K110" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L110" s="3" t="s">
-        <v>401</v>
+        <v>390</v>
       </c>
       <c r="M110" s="1" t="s">
-        <v>400</v>
+        <v>389</v>
       </c>
     </row>
     <row r="111" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="25"/>
         <v>106</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>334</v>
+        <v>323</v>
       </c>
       <c r="C111" s="3"/>
       <c r="D111" s="3" t="s">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="E111" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F111" s="3" t="s">
-        <v>303</v>
+        <v>338</v>
       </c>
       <c r="G111" s="3" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="H111" s="3">
-        <v>2528098284</v>
+        <v>2525322323</v>
       </c>
       <c r="I111" s="3">
-        <v>572004402</v>
+        <v>550101168</v>
       </c>
       <c r="J111" s="3" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="K111" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L111" s="3" t="s">
-        <v>401</v>
+        <v>390</v>
       </c>
       <c r="M111" s="1" t="s">
-        <v>400</v>
+        <v>389</v>
       </c>
     </row>
     <row r="112" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="25"/>
         <v>107</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>334</v>
+        <v>323</v>
       </c>
       <c r="C112" s="3"/>
       <c r="D112" s="3" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="E112" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F112" s="3" t="s">
-        <v>230</v>
+      <c r="F112" s="18">
+        <v>45849</v>
       </c>
       <c r="G112" s="3" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="H112" s="3">
-        <v>2536636620</v>
+        <v>2619139245</v>
       </c>
       <c r="I112" s="3">
-        <v>549284079</v>
+        <v>574631281</v>
       </c>
       <c r="J112" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="K112" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L112" s="3" t="s">
-        <v>401</v>
+        <v>390</v>
       </c>
       <c r="M112" s="1" t="s">
-        <v>400</v>
+        <v>389</v>
       </c>
     </row>
     <row r="113" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="25"/>
         <v>108</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>334</v>
+        <v>323</v>
       </c>
       <c r="C113" s="3"/>
       <c r="D113" s="3" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="E113" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F113" s="3" t="s">
-        <v>349</v>
+        <v>5</v>
+      </c>
+      <c r="F113" s="18">
+        <v>45699</v>
       </c>
       <c r="G113" s="3" t="s">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="H113" s="3">
-        <v>2525322323</v>
+        <v>2515765085</v>
       </c>
       <c r="I113" s="3">
-        <v>550101168</v>
+        <v>506100463</v>
       </c>
       <c r="J113" s="3" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="K113" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L113" s="3" t="s">
-        <v>401</v>
+        <v>390</v>
       </c>
       <c r="M113" s="1" t="s">
-        <v>400</v>
+        <v>389</v>
       </c>
     </row>
     <row r="114" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="25"/>
         <v>109</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>334</v>
+        <v>323</v>
       </c>
       <c r="C114" s="3"/>
       <c r="D114" s="3" t="s">
-        <v>351</v>
+        <v>344</v>
       </c>
       <c r="E114" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F114" s="18">
-        <v>45849</v>
+      <c r="F114" s="3" t="s">
+        <v>265</v>
       </c>
       <c r="G114" s="3" t="s">
-        <v>352</v>
+        <v>345</v>
       </c>
       <c r="H114" s="3">
-        <v>2619139245</v>
+        <v>2619027036</v>
       </c>
       <c r="I114" s="3">
-        <v>574631281</v>
+        <v>565213845</v>
       </c>
       <c r="J114" s="3" t="s">
-        <v>224</v>
+        <v>197</v>
       </c>
       <c r="K114" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L114" s="3" t="s">
-        <v>401</v>
+        <v>390</v>
       </c>
       <c r="M114" s="1" t="s">
-        <v>400</v>
+        <v>389</v>
       </c>
     </row>
     <row r="115" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="25"/>
         <v>110</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>334</v>
+        <v>323</v>
       </c>
       <c r="C115" s="3"/>
       <c r="D115" s="3" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="E115" s="3" t="s">
         <v>5</v>
       </c>
       <c r="F115" s="18">
-        <v>45699</v>
+        <v>45971</v>
       </c>
       <c r="G115" s="3" t="s">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="H115" s="3">
-        <v>2515765085</v>
+        <v>2619035443</v>
       </c>
       <c r="I115" s="3">
-        <v>506100463</v>
+        <v>545671986</v>
       </c>
       <c r="J115" s="3" t="s">
-        <v>224</v>
+        <v>197</v>
       </c>
       <c r="K115" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L115" s="3" t="s">
-        <v>401</v>
+        <v>390</v>
       </c>
       <c r="M115" s="1" t="s">
-        <v>400</v>
+        <v>389</v>
       </c>
     </row>
     <row r="116" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="25"/>
         <v>111</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>334</v>
+        <v>12</v>
       </c>
       <c r="C116" s="3"/>
       <c r="D116" s="3" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="E116" s="3" t="s">
         <v>5</v>
       </c>
       <c r="F116" s="3" t="s">
-        <v>275</v>
+        <v>349</v>
       </c>
       <c r="G116" s="3" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="H116" s="3">
-        <v>2619027036</v>
+        <v>2619744895</v>
       </c>
       <c r="I116" s="3">
-        <v>565213845</v>
+        <v>573345451</v>
       </c>
       <c r="J116" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="K116" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L116" s="3" t="s">
-        <v>401</v>
+        <v>412</v>
       </c>
       <c r="M116" s="1" t="s">
-        <v>400</v>
+        <v>190</v>
       </c>
     </row>
     <row r="117" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="25"/>
         <v>112</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>334</v>
+        <v>12</v>
       </c>
       <c r="C117" s="3"/>
       <c r="D117" s="3" t="s">
-        <v>357</v>
+        <v>348</v>
       </c>
       <c r="E117" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F117" s="18">
-        <v>45971</v>
+        <v>10</v>
+      </c>
+      <c r="F117" s="3" t="s">
+        <v>351</v>
       </c>
       <c r="G117" s="3" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="H117" s="3">
-        <v>2619035443</v>
+        <v>2509942500</v>
       </c>
       <c r="I117" s="3">
-        <v>545671986</v>
+        <v>595007517</v>
       </c>
       <c r="J117" s="3" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="K117" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L117" s="3" t="s">
-        <v>401</v>
+        <v>412</v>
       </c>
       <c r="M117" s="1" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
     </row>
     <row r="118" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="A118:A182" si="26">A117+1</f>
         <v>113</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>12</v>
+        <v>353</v>
       </c>
       <c r="C118" s="3"/>
       <c r="D118" s="3" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="E118" s="3" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F118" s="3" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="G118" s="3" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="H118" s="3">
-        <v>2619744895</v>
+        <v>2282140603</v>
       </c>
       <c r="I118" s="3">
-        <v>573345451</v>
+        <v>582685285</v>
       </c>
       <c r="J118" s="3" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="K118" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L118" s="3" t="s">
-        <v>423</v>
+        <v>388</v>
       </c>
       <c r="M118" s="1" t="s">
-        <v>200</v>
+        <v>473</v>
       </c>
     </row>
     <row r="119" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="26"/>
         <v>114</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>12</v>
+        <v>353</v>
       </c>
       <c r="C119" s="3"/>
       <c r="D119" s="3" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="E119" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F119" s="3" t="s">
-        <v>362</v>
+      <c r="F119" s="18">
+        <v>45668</v>
       </c>
       <c r="G119" s="3" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="H119" s="3">
-        <v>2509942500</v>
+        <v>2596987046</v>
       </c>
       <c r="I119" s="3">
-        <v>595007517</v>
+        <v>556988467</v>
       </c>
       <c r="J119" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="K119" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L119" s="3" t="s">
-        <v>423</v>
+        <v>388</v>
       </c>
       <c r="M119" s="1" t="s">
-        <v>405</v>
+        <v>473</v>
       </c>
     </row>
     <row r="120" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="1">
-        <f t="shared" ref="A120:A183" si="3">A119+1</f>
+        <f t="shared" si="26"/>
         <v>115</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>364</v>
+        <v>353</v>
       </c>
       <c r="C120" s="3"/>
       <c r="D120" s="3" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="E120" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F120" s="3" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="G120" s="3" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="H120" s="3">
-        <v>2282140603</v>
+        <v>2617997859</v>
       </c>
       <c r="I120" s="3">
-        <v>582685285</v>
+        <v>572228053</v>
       </c>
       <c r="J120" s="3" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="K120" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L120" s="3" t="s">
-        <v>399</v>
+        <v>388</v>
       </c>
       <c r="M120" s="1" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
     </row>
     <row r="121" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="26"/>
         <v>116</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>364</v>
+        <v>353</v>
       </c>
       <c r="C121" s="3"/>
       <c r="D121" s="3" t="s">
-        <v>368</v>
+        <v>359</v>
       </c>
       <c r="E121" s="3" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F121" s="18">
-        <v>45668</v>
+        <v>45727</v>
       </c>
       <c r="G121" s="3" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="H121" s="3">
-        <v>2596987046</v>
+        <v>2524756125</v>
       </c>
       <c r="I121" s="3">
-        <v>556988467</v>
+        <v>530920398</v>
       </c>
       <c r="J121" s="3" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="K121" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L121" s="3" t="s">
-        <v>399</v>
+        <v>388</v>
       </c>
       <c r="M121" s="1" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
     </row>
     <row r="122" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="26"/>
         <v>117</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>364</v>
+        <v>353</v>
       </c>
       <c r="C122" s="3"/>
       <c r="D122" s="3" t="s">
-        <v>370</v>
+        <v>363</v>
       </c>
       <c r="E122" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F122" s="3" t="s">
-        <v>371</v>
+      <c r="F122" s="18">
+        <v>45668</v>
       </c>
       <c r="G122" s="3" t="s">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="H122" s="3">
-        <v>2617997859</v>
+        <v>2598963912</v>
       </c>
       <c r="I122" s="3">
-        <v>572228053</v>
+        <v>569036332</v>
       </c>
       <c r="J122" s="3" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="K122" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L122" s="3" t="s">
-        <v>399</v>
+        <v>388</v>
       </c>
       <c r="M122" s="1" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
     </row>
     <row r="123" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="26"/>
         <v>118</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>364</v>
+        <v>353</v>
       </c>
       <c r="C123" s="3"/>
       <c r="D123" s="3" t="s">
-        <v>370</v>
+        <v>363</v>
       </c>
       <c r="E123" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F123" s="18">
-        <v>45727</v>
+      <c r="F123" s="3" t="s">
+        <v>267</v>
       </c>
       <c r="G123" s="3" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="H123" s="3">
-        <v>2524756125</v>
+        <v>2614014401</v>
       </c>
       <c r="I123" s="3">
-        <v>530920398</v>
+        <v>577584350</v>
       </c>
       <c r="J123" s="3" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="K123" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L123" s="3" t="s">
-        <v>399</v>
+        <v>388</v>
       </c>
       <c r="M123" s="1" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
     </row>
     <row r="124" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="26"/>
         <v>119</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>364</v>
+        <v>353</v>
       </c>
       <c r="C124" s="3"/>
       <c r="D124" s="3" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="E124" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F124" s="18">
-        <v>45668</v>
+      <c r="F124" s="3" t="s">
+        <v>360</v>
       </c>
       <c r="G124" s="3" t="s">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="H124" s="3">
-        <v>2598963912</v>
+        <v>2617998089</v>
       </c>
       <c r="I124" s="3">
-        <v>569036332</v>
+        <v>571157356</v>
       </c>
       <c r="J124" s="3" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="K124" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L124" s="3" t="s">
-        <v>399</v>
+        <v>388</v>
       </c>
       <c r="M124" s="1" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
     </row>
     <row r="125" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="26"/>
         <v>120</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>364</v>
+        <v>353</v>
       </c>
       <c r="C125" s="3"/>
       <c r="D125" s="3" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="E125" s="3" t="s">
         <v>5</v>
       </c>
       <c r="F125" s="3" t="s">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="G125" s="3" t="s">
-        <v>376</v>
+        <v>368</v>
       </c>
       <c r="H125" s="3">
-        <v>2614014401</v>
+        <v>2595625779</v>
       </c>
       <c r="I125" s="3">
-        <v>577584350</v>
+        <v>597391804</v>
       </c>
       <c r="J125" s="3" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="K125" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L125" s="3" t="s">
-        <v>399</v>
+        <v>388</v>
       </c>
       <c r="M125" s="1" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
     </row>
     <row r="126" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="26"/>
         <v>121</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>364</v>
+        <v>353</v>
       </c>
       <c r="C126" s="3"/>
       <c r="D126" s="3" t="s">
-        <v>377</v>
+        <v>369</v>
       </c>
       <c r="E126" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F126" s="3" t="s">
-        <v>371</v>
+      <c r="F126" s="18">
+        <v>45999</v>
       </c>
       <c r="G126" s="3" t="s">
-        <v>378</v>
+        <v>370</v>
       </c>
       <c r="H126" s="3">
-        <v>2617998089</v>
+        <v>2609006933</v>
       </c>
       <c r="I126" s="3">
-        <v>571157356</v>
+        <v>507617386</v>
       </c>
       <c r="J126" s="3" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="K126" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L126" s="3" t="s">
-        <v>399</v>
+        <v>388</v>
       </c>
       <c r="M126" s="1" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
     </row>
     <row r="127" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="26"/>
         <v>122</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>364</v>
+        <v>353</v>
       </c>
       <c r="C127" s="3"/>
       <c r="D127" s="3" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="E127" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F127" s="3" t="s">
-        <v>277</v>
+        <v>10</v>
+      </c>
+      <c r="F127" s="18">
+        <v>45727</v>
       </c>
       <c r="G127" s="3" t="s">
-        <v>379</v>
+        <v>372</v>
       </c>
       <c r="H127" s="3">
-        <v>2595625779</v>
+        <v>2524757180</v>
       </c>
       <c r="I127" s="3">
-        <v>597391804</v>
+        <v>534063139</v>
       </c>
       <c r="J127" s="3" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="K127" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L127" s="3" t="s">
-        <v>399</v>
+        <v>388</v>
       </c>
       <c r="M127" s="1" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
     </row>
     <row r="128" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="26"/>
         <v>123</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>364</v>
+        <v>353</v>
       </c>
       <c r="C128" s="3"/>
       <c r="D128" s="3" t="s">
-        <v>380</v>
+        <v>373</v>
       </c>
       <c r="E128" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F128" s="18">
-        <v>45999</v>
+        <v>45907</v>
       </c>
       <c r="G128" s="3" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="H128" s="3">
-        <v>2609006933</v>
+        <v>2344941238</v>
       </c>
       <c r="I128" s="3">
-        <v>507617386</v>
+        <v>596717285</v>
       </c>
       <c r="J128" s="3" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="K128" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L128" s="3" t="s">
-        <v>399</v>
+        <v>388</v>
       </c>
       <c r="M128" s="1" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
     </row>
     <row r="129" spans="1:18" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="26"/>
         <v>124</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>364</v>
+        <v>375</v>
       </c>
       <c r="C129" s="3"/>
       <c r="D129" s="3" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="E129" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F129" s="18">
-        <v>45727</v>
+        <v>5</v>
+      </c>
+      <c r="F129" s="3" t="s">
+        <v>377</v>
       </c>
       <c r="G129" s="3" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="H129" s="3">
-        <v>2524757180</v>
+        <v>2522755632</v>
       </c>
       <c r="I129" s="3">
-        <v>534063139</v>
+        <v>572991664</v>
       </c>
       <c r="J129" s="3" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="K129" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L129" s="3" t="s">
-        <v>399</v>
+        <v>433</v>
       </c>
       <c r="M129" s="1" t="s">
-        <v>484</v>
+        <v>434</v>
       </c>
     </row>
     <row r="130" spans="1:18" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="26"/>
         <v>125</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>364</v>
+        <v>375</v>
       </c>
       <c r="C130" s="3"/>
       <c r="D130" s="3" t="s">
         <v>384</v>
       </c>
       <c r="E130" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F130" s="18">
-        <v>45907</v>
+        <v>5</v>
+      </c>
+      <c r="F130" s="3" t="s">
+        <v>385</v>
       </c>
       <c r="G130" s="3" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H130" s="3">
-        <v>2344941238</v>
+        <v>2530061957</v>
       </c>
       <c r="I130" s="3">
-        <v>596717285</v>
+        <v>533427252</v>
       </c>
       <c r="J130" s="3" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="K130" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L130" s="3" t="s">
-        <v>399</v>
+        <v>390</v>
       </c>
       <c r="M130" s="1" t="s">
-        <v>484</v>
+        <v>190</v>
       </c>
     </row>
     <row r="131" spans="1:18" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="26"/>
         <v>126</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="C131" s="3"/>
       <c r="D131" s="3" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
       <c r="E131" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F131" s="3" t="s">
-        <v>388</v>
-      </c>
+      <c r="F131" s="3"/>
       <c r="G131" s="3" t="s">
-        <v>389</v>
+        <v>407</v>
       </c>
       <c r="H131" s="3">
-        <v>2522755632</v>
+        <v>2371258480</v>
       </c>
       <c r="I131" s="3">
-        <v>572991664</v>
+        <v>1</v>
       </c>
       <c r="J131" s="3" t="s">
-        <v>224</v>
+        <v>197</v>
       </c>
       <c r="K131" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L131" s="3" t="s">
-        <v>444</v>
+        <v>412</v>
       </c>
       <c r="M131" s="1" t="s">
-        <v>445</v>
+        <v>469</v>
       </c>
     </row>
     <row r="132" spans="1:18" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="26"/>
         <v>127</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="C132" s="3"/>
       <c r="D132" s="3" t="s">
-        <v>395</v>
+        <v>380</v>
       </c>
       <c r="E132" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F132" s="3" t="s">
-        <v>396</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="F132" s="3"/>
       <c r="G132" s="3" t="s">
-        <v>397</v>
+        <v>381</v>
       </c>
       <c r="H132" s="3">
-        <v>2530061957</v>
+        <v>2545277937</v>
       </c>
       <c r="I132" s="3">
-        <v>533427252</v>
+        <v>1</v>
       </c>
       <c r="J132" s="3" t="s">
-        <v>224</v>
+        <v>197</v>
       </c>
       <c r="K132" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L132" s="3" t="s">
-        <v>401</v>
+        <v>412</v>
       </c>
       <c r="M132" s="1" t="s">
-        <v>200</v>
+        <v>470</v>
       </c>
     </row>
     <row r="133" spans="1:18" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="26"/>
         <v>128</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>390</v>
+        <v>379</v>
       </c>
       <c r="C133" s="3"/>
       <c r="D133" s="3" t="s">
-        <v>391</v>
+        <v>382</v>
       </c>
       <c r="E133" s="3" t="s">
         <v>5</v>
       </c>
       <c r="F133" s="3"/>
       <c r="G133" s="3" t="s">
-        <v>418</v>
+        <v>408</v>
       </c>
       <c r="H133" s="3">
-        <v>2371258480</v>
+        <v>2510755784</v>
       </c>
       <c r="I133" s="3">
         <v>1</v>
       </c>
       <c r="J133" s="3" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="K133" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L133" s="3" t="s">
-        <v>423</v>
+        <v>412</v>
       </c>
       <c r="M133" s="1" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="134" spans="1:18" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="26"/>
         <v>129</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>390</v>
+        <v>379</v>
       </c>
       <c r="C134" s="3"/>
       <c r="D134" s="3" t="s">
-        <v>391</v>
+        <v>382</v>
       </c>
       <c r="E134" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F134" s="3"/>
       <c r="G134" s="3" t="s">
-        <v>392</v>
+        <v>409</v>
       </c>
       <c r="H134" s="3">
-        <v>2545277937</v>
+        <v>2402689315</v>
       </c>
       <c r="I134" s="3">
         <v>1</v>
       </c>
       <c r="J134" s="3" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="K134" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L134" s="3" t="s">
-        <v>423</v>
+        <v>412</v>
       </c>
       <c r="M134" s="1" t="s">
-        <v>481</v>
+        <v>472</v>
       </c>
     </row>
     <row r="135" spans="1:18" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="26"/>
         <v>130</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>390</v>
+        <v>379</v>
       </c>
       <c r="C135" s="3"/>
       <c r="D135" s="3" t="s">
-        <v>393</v>
+        <v>383</v>
       </c>
       <c r="E135" s="3" t="s">
         <v>5</v>
       </c>
       <c r="F135" s="3"/>
       <c r="G135" s="3" t="s">
-        <v>419</v>
+        <v>410</v>
       </c>
       <c r="H135" s="3">
-        <v>2510755784</v>
+        <v>2602788081</v>
       </c>
       <c r="I135" s="3">
         <v>1</v>
       </c>
       <c r="J135" s="3" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="K135" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L135" s="3" t="s">
-        <v>423</v>
+        <v>412</v>
       </c>
       <c r="M135" s="1" t="s">
-        <v>482</v>
+        <v>471</v>
       </c>
     </row>
     <row r="136" spans="1:18" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A136" s="1">
-        <f t="shared" si="3"/>
+      <c r="A136" s="11">
+        <f t="shared" si="26"/>
         <v>131</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>390</v>
+        <v>379</v>
       </c>
       <c r="C136" s="3"/>
       <c r="D136" s="3" t="s">
-        <v>393</v>
+        <v>383</v>
       </c>
       <c r="E136" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F136" s="3"/>
       <c r="G136" s="3" t="s">
-        <v>420</v>
+        <v>411</v>
       </c>
       <c r="H136" s="3">
-        <v>2402689315</v>
+        <v>2293294985</v>
       </c>
       <c r="I136" s="3">
         <v>1</v>
       </c>
       <c r="J136" s="3" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="K136" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L136" s="3" t="s">
-        <v>423</v>
+        <v>412</v>
       </c>
       <c r="M136" s="1" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="137" spans="1:18" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A137" s="1">
-        <f t="shared" si="3"/>
+        <v>472</v>
+      </c>
+    </row>
+    <row r="137" spans="1:18" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A137" s="11">
+        <f t="shared" si="26"/>
         <v>132</v>
       </c>
-      <c r="B137" s="3" t="s">
-        <v>390</v>
+      <c r="B137" s="12" t="s">
+        <v>468</v>
       </c>
       <c r="C137" s="3"/>
-      <c r="D137" s="3" t="s">
-        <v>394</v>
+      <c r="D137" s="12">
+        <v>503001447</v>
       </c>
       <c r="E137" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F137" s="18">
+        <v>45669</v>
+      </c>
+      <c r="G137" s="19" t="s">
+        <v>454</v>
+      </c>
+      <c r="H137" s="3">
+        <v>2619033927</v>
+      </c>
+      <c r="I137" s="12">
+        <v>552218662</v>
+      </c>
+      <c r="J137" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="K137" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="L137" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="M137" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="N137" s="2"/>
+      <c r="O137" s="2"/>
+      <c r="P137" s="2"/>
+      <c r="Q137" s="2"/>
+      <c r="R137" s="2"/>
+    </row>
+    <row r="138" spans="1:18" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A138" s="11">
+        <f t="shared" si="26"/>
+        <v>133</v>
+      </c>
+      <c r="B138" s="12" t="s">
+        <v>468</v>
+      </c>
+      <c r="C138" s="3"/>
+      <c r="D138" s="12">
+        <v>503001447</v>
+      </c>
+      <c r="E138" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F137" s="3"/>
-      <c r="G137" s="3" t="s">
-        <v>421</v>
-      </c>
-      <c r="H137" s="3">
-        <v>2602788081</v>
-      </c>
-      <c r="I137" s="3">
-        <v>1</v>
-      </c>
-      <c r="J137" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="K137" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="L137" s="3" t="s">
-        <v>423</v>
-      </c>
-      <c r="M137" s="1" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="138" spans="1:18" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A138" s="11">
-        <f t="shared" si="3"/>
-        <v>133</v>
-      </c>
-      <c r="B138" s="3" t="s">
-        <v>390</v>
-      </c>
-      <c r="C138" s="3"/>
-      <c r="D138" s="3" t="s">
-        <v>394</v>
-      </c>
-      <c r="E138" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F138" s="3"/>
-      <c r="G138" s="3" t="s">
-        <v>422</v>
+      <c r="F138" s="18">
+        <v>45670</v>
+      </c>
+      <c r="G138" s="19" t="s">
+        <v>455</v>
       </c>
       <c r="H138" s="3">
-        <v>2293294985</v>
-      </c>
-      <c r="I138" s="3">
-        <v>1</v>
+        <v>2619034537</v>
+      </c>
+      <c r="I138" s="12">
+        <v>581669127</v>
       </c>
       <c r="J138" s="3" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="K138" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L138" s="3" t="s">
-        <v>423</v>
+        <v>412</v>
       </c>
       <c r="M138" s="1" t="s">
-        <v>483</v>
-      </c>
+        <v>462</v>
+      </c>
+      <c r="N138" s="2"/>
+      <c r="O138" s="2"/>
+      <c r="P138" s="2"/>
+      <c r="Q138" s="2"/>
+      <c r="R138" s="2"/>
     </row>
     <row r="139" spans="1:18" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A139" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="26"/>
         <v>134</v>
       </c>
       <c r="B139" s="12" t="s">
-        <v>479</v>
+        <v>468</v>
       </c>
       <c r="C139" s="3"/>
       <c r="D139" s="12">
-        <v>503001447</v>
+        <v>503001383</v>
       </c>
       <c r="E139" s="3" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F139" s="18">
-        <v>45669</v>
+        <v>45671</v>
       </c>
       <c r="G139" s="19" t="s">
-        <v>465</v>
+        <v>456</v>
       </c>
       <c r="H139" s="3">
-        <v>2619033927</v>
+        <v>2529002384</v>
       </c>
       <c r="I139" s="12">
-        <v>552218662</v>
+        <v>558533083</v>
       </c>
       <c r="J139" s="3" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="K139" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L139" s="3" t="s">
-        <v>423</v>
+        <v>412</v>
       </c>
       <c r="M139" s="1" t="s">
-        <v>473</v>
+        <v>462</v>
       </c>
       <c r="N139" s="2"/>
       <c r="O139" s="2"/>
@@ -8239,42 +8251,42 @@
     </row>
     <row r="140" spans="1:18" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A140" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="26"/>
         <v>135</v>
       </c>
       <c r="B140" s="12" t="s">
-        <v>479</v>
+        <v>468</v>
       </c>
       <c r="C140" s="3"/>
-      <c r="D140" s="12">
-        <v>503001447</v>
+      <c r="D140" s="12" t="s">
+        <v>448</v>
       </c>
       <c r="E140" s="3" t="s">
         <v>5</v>
       </c>
       <c r="F140" s="18">
-        <v>45670</v>
+        <v>45672</v>
       </c>
       <c r="G140" s="19" t="s">
-        <v>466</v>
+        <v>457</v>
       </c>
       <c r="H140" s="3">
-        <v>2619034537</v>
+        <v>2619027200</v>
       </c>
       <c r="I140" s="12">
-        <v>581669127</v>
+        <v>572385247</v>
       </c>
       <c r="J140" s="3" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="K140" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L140" s="3" t="s">
-        <v>423</v>
+        <v>412</v>
       </c>
       <c r="M140" s="1" t="s">
-        <v>473</v>
+        <v>462</v>
       </c>
       <c r="N140" s="2"/>
       <c r="O140" s="2"/>
@@ -8284,280 +8296,268 @@
     </row>
     <row r="141" spans="1:18" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A141" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="26"/>
         <v>136</v>
       </c>
       <c r="B141" s="12" t="s">
-        <v>479</v>
+        <v>449</v>
       </c>
       <c r="C141" s="3"/>
-      <c r="D141" s="12">
-        <v>503001383</v>
+      <c r="D141" s="12" t="s">
+        <v>450</v>
       </c>
       <c r="E141" s="3" t="s">
         <v>5</v>
       </c>
       <c r="F141" s="18">
-        <v>45671</v>
+        <v>45673</v>
       </c>
       <c r="G141" s="19" t="s">
-        <v>467</v>
+        <v>458</v>
       </c>
       <c r="H141" s="3">
-        <v>2529002384</v>
+        <v>2619097583</v>
       </c>
       <c r="I141" s="12">
-        <v>558533083</v>
+        <v>563245681</v>
       </c>
       <c r="J141" s="3" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="K141" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L141" s="3" t="s">
-        <v>423</v>
+        <v>412</v>
       </c>
       <c r="M141" s="1" t="s">
-        <v>473</v>
-      </c>
-      <c r="N141" s="2"/>
-      <c r="O141" s="2"/>
-      <c r="P141" s="2"/>
-      <c r="Q141" s="2"/>
-      <c r="R141" s="2"/>
+        <v>462</v>
+      </c>
     </row>
     <row r="142" spans="1:18" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A142" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="26"/>
         <v>137</v>
       </c>
       <c r="B142" s="12" t="s">
-        <v>479</v>
+        <v>449</v>
       </c>
       <c r="C142" s="3"/>
       <c r="D142" s="12" t="s">
-        <v>459</v>
+        <v>451</v>
       </c>
       <c r="E142" s="3" t="s">
         <v>5</v>
       </c>
       <c r="F142" s="18">
-        <v>45672</v>
+        <v>45674</v>
       </c>
       <c r="G142" s="19" t="s">
-        <v>468</v>
+        <v>459</v>
       </c>
       <c r="H142" s="3">
-        <v>2619027200</v>
+        <v>2621447321</v>
       </c>
       <c r="I142" s="12">
-        <v>572385247</v>
+        <v>531682160</v>
       </c>
       <c r="J142" s="3" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="K142" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L142" s="3" t="s">
-        <v>423</v>
+        <v>412</v>
       </c>
       <c r="M142" s="1" t="s">
-        <v>473</v>
-      </c>
-      <c r="N142" s="2"/>
-      <c r="O142" s="2"/>
-      <c r="P142" s="2"/>
-      <c r="Q142" s="2"/>
-      <c r="R142" s="2"/>
+        <v>462</v>
+      </c>
     </row>
     <row r="143" spans="1:18" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A143" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="26"/>
         <v>138</v>
       </c>
       <c r="B143" s="12" t="s">
-        <v>460</v>
+        <v>449</v>
       </c>
       <c r="C143" s="3"/>
       <c r="D143" s="12" t="s">
-        <v>461</v>
+        <v>452</v>
       </c>
       <c r="E143" s="3" t="s">
         <v>5</v>
       </c>
       <c r="F143" s="18">
-        <v>45673</v>
+        <v>45675</v>
       </c>
       <c r="G143" s="19" t="s">
-        <v>469</v>
+        <v>460</v>
       </c>
       <c r="H143" s="3">
-        <v>2619097583</v>
+        <v>2621465323</v>
       </c>
       <c r="I143" s="12">
-        <v>563245681</v>
+        <v>550925696</v>
       </c>
       <c r="J143" s="3" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="K143" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L143" s="3" t="s">
-        <v>423</v>
+        <v>412</v>
       </c>
       <c r="M143" s="1" t="s">
-        <v>473</v>
+        <v>462</v>
       </c>
     </row>
     <row r="144" spans="1:18" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A144" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="26"/>
         <v>139</v>
       </c>
       <c r="B144" s="12" t="s">
-        <v>460</v>
+        <v>449</v>
       </c>
       <c r="C144" s="3"/>
       <c r="D144" s="12" t="s">
-        <v>462</v>
+        <v>453</v>
       </c>
       <c r="E144" s="3" t="s">
         <v>5</v>
       </c>
       <c r="F144" s="18">
-        <v>45674</v>
+        <v>45676</v>
       </c>
       <c r="G144" s="19" t="s">
-        <v>470</v>
+        <v>461</v>
       </c>
       <c r="H144" s="3">
-        <v>2621447321</v>
+        <v>2619028604</v>
       </c>
       <c r="I144" s="12">
-        <v>531682160</v>
+        <v>552113039</v>
       </c>
       <c r="J144" s="3" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="K144" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L144" s="3" t="s">
-        <v>423</v>
+        <v>412</v>
       </c>
       <c r="M144" s="1" t="s">
-        <v>473</v>
+        <v>462</v>
       </c>
     </row>
     <row r="145" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A145" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="26"/>
         <v>140</v>
       </c>
-      <c r="B145" s="12" t="s">
-        <v>460</v>
+      <c r="B145" s="3" t="s">
+        <v>148</v>
       </c>
       <c r="C145" s="3"/>
-      <c r="D145" s="12" t="s">
+      <c r="D145" s="3" t="s">
         <v>463</v>
       </c>
       <c r="E145" s="3" t="s">
         <v>5</v>
       </c>
       <c r="F145" s="18">
-        <v>45675</v>
-      </c>
-      <c r="G145" s="19" t="s">
-        <v>471</v>
+        <v>45677</v>
+      </c>
+      <c r="G145" s="3" t="s">
+        <v>464</v>
       </c>
       <c r="H145" s="3">
-        <v>2621465323</v>
-      </c>
-      <c r="I145" s="12">
-        <v>550925696</v>
+        <v>2550483701</v>
+      </c>
+      <c r="I145" s="3">
+        <v>502179038</v>
       </c>
       <c r="J145" s="3" t="s">
-        <v>207</v>
+        <v>43</v>
       </c>
       <c r="K145" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L145" s="3" t="s">
-        <v>423</v>
+        <v>412</v>
       </c>
       <c r="M145" s="1" t="s">
-        <v>473</v>
+        <v>462</v>
       </c>
     </row>
     <row r="146" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A146" s="11">
-        <f t="shared" si="3"/>
+      <c r="A146" s="1">
+        <f t="shared" si="26"/>
         <v>141</v>
       </c>
-      <c r="B146" s="12" t="s">
-        <v>460</v>
+      <c r="B146" s="3" t="s">
+        <v>466</v>
       </c>
       <c r="C146" s="3"/>
-      <c r="D146" s="12" t="s">
-        <v>464</v>
+      <c r="D146" s="3" t="s">
+        <v>467</v>
       </c>
       <c r="E146" s="3" t="s">
         <v>5</v>
       </c>
       <c r="F146" s="18">
-        <v>45676</v>
-      </c>
-      <c r="G146" s="19" t="s">
-        <v>472</v>
+        <v>45678</v>
+      </c>
+      <c r="G146" s="3" t="s">
+        <v>465</v>
       </c>
       <c r="H146" s="3">
-        <v>2619028604</v>
-      </c>
-      <c r="I146" s="12">
-        <v>552113039</v>
+        <v>2622079818</v>
+      </c>
+      <c r="I146" s="3">
+        <v>573380318</v>
       </c>
       <c r="J146" s="3" t="s">
-        <v>207</v>
+        <v>138</v>
       </c>
       <c r="K146" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L146" s="3" t="s">
-        <v>423</v>
+        <v>412</v>
       </c>
       <c r="M146" s="1" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
     </row>
     <row r="147" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A147" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="26"/>
         <v>142</v>
       </c>
-      <c r="B147" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="C147" s="3"/>
-      <c r="D147" s="3" t="s">
-        <v>474</v>
+      <c r="B147" s="12" t="s">
+        <v>449</v>
+      </c>
+      <c r="C147" s="17"/>
+      <c r="D147" s="20" t="s">
+        <v>70</v>
       </c>
       <c r="E147" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F147" s="18">
-        <v>45677</v>
-      </c>
-      <c r="G147" s="3" t="s">
+      <c r="F147" s="17"/>
+      <c r="G147" s="19" t="s">
         <v>475</v>
       </c>
       <c r="H147" s="3">
-        <v>2550483701</v>
-      </c>
-      <c r="I147" s="3">
-        <v>502179038</v>
+        <v>2534900234</v>
+      </c>
+      <c r="I147" s="12">
+        <v>575295148</v>
       </c>
       <c r="J147" s="3" t="s">
         <v>43</v>
@@ -8566,1126 +8566,1180 @@
         <v>9</v>
       </c>
       <c r="L147" s="3" t="s">
-        <v>423</v>
+        <v>412</v>
       </c>
       <c r="M147" s="1" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="148" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A148" s="1">
-        <f t="shared" si="3"/>
+        <v>476</v>
+      </c>
+    </row>
+    <row r="148" spans="1:13" ht="27" x14ac:dyDescent="0.25">
+      <c r="A148" s="11">
+        <f t="shared" si="26"/>
         <v>143</v>
       </c>
-      <c r="B148" s="3" t="s">
+      <c r="B148" s="21" t="s">
         <v>477</v>
       </c>
-      <c r="C148" s="3"/>
-      <c r="D148" s="3" t="s">
+      <c r="C148" s="17"/>
+      <c r="D148" s="21" t="s">
         <v>478</v>
       </c>
-      <c r="E148" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F148" s="18">
-        <v>45678</v>
-      </c>
-      <c r="G148" s="3" t="s">
-        <v>476</v>
-      </c>
-      <c r="H148" s="3">
-        <v>2622079818</v>
-      </c>
-      <c r="I148" s="3">
-        <v>573380318</v>
-      </c>
-      <c r="J148" s="3" t="s">
-        <v>147</v>
+      <c r="E148" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="F148" s="17"/>
+      <c r="G148" s="20" t="s">
+        <v>481</v>
+      </c>
+      <c r="H148" s="20">
+        <v>2563844956</v>
+      </c>
+      <c r="I148" s="20">
+        <v>539475406</v>
+      </c>
+      <c r="J148" s="20" t="s">
+        <v>487</v>
       </c>
       <c r="K148" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="L148" s="3" t="s">
-        <v>423</v>
-      </c>
-      <c r="M148" s="1" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="149" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="L148" s="20" t="s">
+        <v>488</v>
+      </c>
+      <c r="M148" s="23" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="149" spans="1:13" ht="27" x14ac:dyDescent="0.25">
       <c r="A149" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="26"/>
         <v>144</v>
       </c>
-      <c r="B149" s="12" t="s">
-        <v>460</v>
+      <c r="B149" s="21" t="s">
+        <v>477</v>
       </c>
       <c r="C149" s="17"/>
-      <c r="D149" s="20" t="s">
-        <v>71</v>
-      </c>
-      <c r="E149" s="3" t="s">
-        <v>5</v>
+      <c r="D149" s="21" t="s">
+        <v>478</v>
+      </c>
+      <c r="E149" s="20" t="s">
+        <v>10</v>
       </c>
       <c r="F149" s="17"/>
-      <c r="G149" s="19" t="s">
-        <v>486</v>
-      </c>
-      <c r="H149" s="3">
-        <v>2534900234</v>
-      </c>
-      <c r="I149" s="12">
-        <v>575295148</v>
-      </c>
-      <c r="J149" s="3" t="s">
-        <v>43</v>
+      <c r="G149" s="20" t="s">
+        <v>482</v>
+      </c>
+      <c r="H149" s="20">
+        <v>2554043436</v>
+      </c>
+      <c r="I149" s="20">
+        <v>508505874</v>
+      </c>
+      <c r="J149" s="20" t="s">
+        <v>487</v>
       </c>
       <c r="K149" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="L149" s="3" t="s">
-        <v>423</v>
-      </c>
-      <c r="M149" s="1" t="s">
-        <v>487</v>
+      <c r="L149" s="20" t="s">
+        <v>488</v>
+      </c>
+      <c r="M149" s="23" t="s">
+        <v>492</v>
       </c>
     </row>
     <row r="150" spans="1:13" ht="27" x14ac:dyDescent="0.25">
       <c r="A150" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="26"/>
         <v>145</v>
       </c>
       <c r="B150" s="21" t="s">
-        <v>488</v>
+        <v>477</v>
       </c>
       <c r="C150" s="17"/>
       <c r="D150" s="21" t="s">
-        <v>489</v>
+        <v>479</v>
       </c>
       <c r="E150" s="20" t="s">
         <v>15</v>
       </c>
       <c r="F150" s="17"/>
       <c r="G150" s="20" t="s">
-        <v>492</v>
+        <v>483</v>
       </c>
       <c r="H150" s="20">
-        <v>2563844956</v>
+        <v>2596902730</v>
       </c>
       <c r="I150" s="20">
-        <v>539475406</v>
+        <v>594534365</v>
       </c>
       <c r="J150" s="20" t="s">
-        <v>498</v>
+        <v>487</v>
       </c>
       <c r="K150" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L150" s="20" t="s">
-        <v>499</v>
+        <v>489</v>
       </c>
       <c r="M150" s="23" t="s">
-        <v>502</v>
+        <v>493</v>
       </c>
     </row>
     <row r="151" spans="1:13" ht="27" x14ac:dyDescent="0.25">
       <c r="A151" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="26"/>
         <v>146</v>
       </c>
       <c r="B151" s="21" t="s">
-        <v>488</v>
+        <v>477</v>
       </c>
       <c r="C151" s="17"/>
       <c r="D151" s="21" t="s">
-        <v>489</v>
+        <v>479</v>
       </c>
       <c r="E151" s="20" t="s">
         <v>10</v>
       </c>
       <c r="F151" s="17"/>
       <c r="G151" s="20" t="s">
+        <v>484</v>
+      </c>
+      <c r="H151" s="20">
+        <v>2609141763</v>
+      </c>
+      <c r="I151" s="20">
+        <v>531693342</v>
+      </c>
+      <c r="J151" s="20" t="s">
+        <v>487</v>
+      </c>
+      <c r="K151" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="L151" s="20" t="s">
+        <v>489</v>
+      </c>
+      <c r="M151" s="23" t="s">
         <v>493</v>
-      </c>
-      <c r="H151" s="20">
-        <v>2554043436</v>
-      </c>
-      <c r="I151" s="20">
-        <v>508505874</v>
-      </c>
-      <c r="J151" s="20" t="s">
-        <v>498</v>
-      </c>
-      <c r="K151" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="L151" s="20" t="s">
-        <v>499</v>
-      </c>
-      <c r="M151" s="23" t="s">
-        <v>502</v>
       </c>
     </row>
     <row r="152" spans="1:13" ht="27" x14ac:dyDescent="0.25">
       <c r="A152" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="26"/>
         <v>147</v>
       </c>
       <c r="B152" s="21" t="s">
-        <v>488</v>
+        <v>477</v>
       </c>
       <c r="C152" s="17"/>
       <c r="D152" s="21" t="s">
-        <v>490</v>
+        <v>480</v>
       </c>
       <c r="E152" s="20" t="s">
         <v>15</v>
       </c>
       <c r="F152" s="17"/>
       <c r="G152" s="20" t="s">
+        <v>485</v>
+      </c>
+      <c r="H152" s="22">
+        <v>2277605909</v>
+      </c>
+      <c r="I152" s="22">
+        <v>597001612</v>
+      </c>
+      <c r="J152" s="22" t="s">
+        <v>487</v>
+      </c>
+      <c r="K152" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="L152" s="20" t="s">
+        <v>490</v>
+      </c>
+      <c r="M152" s="23" t="s">
         <v>494</v>
-      </c>
-      <c r="H152" s="20">
-        <v>2596902730</v>
-      </c>
-      <c r="I152" s="20">
-        <v>594534365</v>
-      </c>
-      <c r="J152" s="20" t="s">
-        <v>498</v>
-      </c>
-      <c r="K152" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="L152" s="20" t="s">
-        <v>500</v>
-      </c>
-      <c r="M152" s="23" t="s">
-        <v>503</v>
       </c>
     </row>
     <row r="153" spans="1:13" ht="27" x14ac:dyDescent="0.25">
       <c r="A153" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="26"/>
         <v>148</v>
       </c>
       <c r="B153" s="21" t="s">
-        <v>488</v>
+        <v>477</v>
       </c>
       <c r="C153" s="17"/>
       <c r="D153" s="21" t="s">
-        <v>490</v>
+        <v>480</v>
       </c>
       <c r="E153" s="20" t="s">
         <v>10</v>
       </c>
       <c r="F153" s="17"/>
       <c r="G153" s="20" t="s">
+        <v>486</v>
+      </c>
+      <c r="H153" s="22">
+        <v>2549390900</v>
+      </c>
+      <c r="I153" s="22">
+        <v>535685417</v>
+      </c>
+      <c r="J153" s="22" t="s">
+        <v>487</v>
+      </c>
+      <c r="K153" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="L153" s="20" t="s">
+        <v>490</v>
+      </c>
+      <c r="M153" s="23" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="154" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A154" s="11">
+        <f t="shared" si="26"/>
+        <v>149</v>
+      </c>
+      <c r="B154" s="21" t="s">
+        <v>477</v>
+      </c>
+      <c r="C154" s="17"/>
+      <c r="D154" s="20" t="s">
         <v>495</v>
       </c>
-      <c r="H153" s="20">
-        <v>2609141763</v>
-      </c>
-      <c r="I153" s="20">
-        <v>531693342</v>
-      </c>
-      <c r="J153" s="20" t="s">
-        <v>498</v>
-      </c>
-      <c r="K153" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="L153" s="20" t="s">
-        <v>500</v>
-      </c>
-      <c r="M153" s="23" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="154" spans="1:13" ht="27" x14ac:dyDescent="0.25">
-      <c r="A154" s="11">
-        <f t="shared" si="3"/>
-        <v>149</v>
-      </c>
-      <c r="B154" s="21" t="s">
-        <v>488</v>
-      </c>
-      <c r="C154" s="17"/>
-      <c r="D154" s="21" t="s">
-        <v>491</v>
-      </c>
-      <c r="E154" s="20" t="s">
-        <v>15</v>
+      <c r="E154" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="F154" s="17"/>
       <c r="G154" s="20" t="s">
         <v>496</v>
       </c>
-      <c r="H154" s="22">
-        <v>2277605909</v>
-      </c>
-      <c r="I154" s="22">
-        <v>597001612</v>
-      </c>
-      <c r="J154" s="22" t="s">
+      <c r="H154" s="20">
+        <v>2518429333</v>
+      </c>
+      <c r="I154" s="20">
+        <v>531689744</v>
+      </c>
+      <c r="J154" s="20" t="s">
         <v>498</v>
       </c>
       <c r="K154" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L154" s="20" t="s">
-        <v>501</v>
-      </c>
-      <c r="M154" s="23" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="155" spans="1:13" ht="27" x14ac:dyDescent="0.25">
+        <v>499</v>
+      </c>
+      <c r="M154" s="17" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="155" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A155" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="26"/>
         <v>150</v>
       </c>
       <c r="B155" s="21" t="s">
-        <v>488</v>
+        <v>477</v>
       </c>
       <c r="C155" s="17"/>
-      <c r="D155" s="21" t="s">
-        <v>491</v>
-      </c>
-      <c r="E155" s="20" t="s">
-        <v>10</v>
+      <c r="D155" s="20" t="s">
+        <v>495</v>
+      </c>
+      <c r="E155" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F155" s="17"/>
       <c r="G155" s="20" t="s">
         <v>497</v>
       </c>
-      <c r="H155" s="22">
-        <v>2549390900</v>
-      </c>
-      <c r="I155" s="22">
-        <v>535685417</v>
-      </c>
-      <c r="J155" s="22" t="s">
+      <c r="H155" s="20">
+        <v>2420273241</v>
+      </c>
+      <c r="I155" s="20">
+        <v>570912540</v>
+      </c>
+      <c r="J155" s="20" t="s">
         <v>498</v>
       </c>
       <c r="K155" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L155" s="20" t="s">
-        <v>501</v>
-      </c>
-      <c r="M155" s="23" t="s">
-        <v>504</v>
+        <v>499</v>
+      </c>
+      <c r="M155" s="17" t="s">
+        <v>500</v>
       </c>
     </row>
     <row r="156" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A156" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="26"/>
         <v>151</v>
       </c>
-      <c r="B156" s="21" t="s">
-        <v>488</v>
-      </c>
-      <c r="C156" s="17"/>
+      <c r="B156" s="20" t="s">
+        <v>501</v>
+      </c>
+      <c r="C156" s="3"/>
       <c r="D156" s="20" t="s">
+        <v>502</v>
+      </c>
+      <c r="E156" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="F156" s="18">
+        <v>45681</v>
+      </c>
+      <c r="G156" s="20" t="s">
         <v>505</v>
       </c>
-      <c r="E156" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F156" s="17"/>
-      <c r="G156" s="20" t="s">
+      <c r="H156" s="20">
+        <v>2611973781</v>
+      </c>
+      <c r="I156" s="20">
+        <v>538841925</v>
+      </c>
+      <c r="J156" s="20" t="s">
+        <v>511</v>
+      </c>
+      <c r="K156" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="L156" s="20" t="s">
+        <v>513</v>
+      </c>
+      <c r="M156" s="23" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="157" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A157" s="11">
+        <f t="shared" si="26"/>
+        <v>152</v>
+      </c>
+      <c r="B157" s="20" t="s">
+        <v>501</v>
+      </c>
+      <c r="C157" s="3"/>
+      <c r="D157" s="20" t="s">
+        <v>502</v>
+      </c>
+      <c r="E157" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="F157" s="18">
+        <v>45682</v>
+      </c>
+      <c r="G157" s="20" t="s">
         <v>506</v>
       </c>
-      <c r="H156" s="20">
-        <v>2518429333</v>
-      </c>
-      <c r="I156" s="20">
-        <v>531689744</v>
-      </c>
-      <c r="J156" s="20" t="s">
-        <v>508</v>
-      </c>
-      <c r="K156" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="L156" s="20" t="s">
-        <v>509</v>
-      </c>
-      <c r="M156" s="17" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="157" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A157" s="11">
-        <f t="shared" si="3"/>
-        <v>152</v>
-      </c>
-      <c r="B157" s="21" t="s">
-        <v>488</v>
-      </c>
-      <c r="C157" s="17"/>
-      <c r="D157" s="20" t="s">
-        <v>505</v>
-      </c>
-      <c r="E157" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F157" s="17"/>
-      <c r="G157" s="20" t="s">
-        <v>507</v>
-      </c>
       <c r="H157" s="20">
-        <v>2420273241</v>
+        <v>2558563686</v>
       </c>
       <c r="I157" s="20">
-        <v>570912540</v>
+        <v>549803297</v>
       </c>
       <c r="J157" s="20" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="K157" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L157" s="20" t="s">
-        <v>509</v>
-      </c>
-      <c r="M157" s="17" t="s">
-        <v>510</v>
+        <v>513</v>
+      </c>
+      <c r="M157" s="23" t="s">
+        <v>515</v>
       </c>
     </row>
     <row r="158" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A158" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="26"/>
         <v>153</v>
       </c>
       <c r="B158" s="20" t="s">
-        <v>511</v>
+        <v>501</v>
       </c>
       <c r="C158" s="3"/>
       <c r="D158" s="20" t="s">
-        <v>512</v>
+        <v>503</v>
       </c>
       <c r="E158" s="20" t="s">
         <v>15</v>
       </c>
       <c r="F158" s="18">
-        <v>45681</v>
+        <v>45683</v>
       </c>
       <c r="G158" s="20" t="s">
+        <v>507</v>
+      </c>
+      <c r="H158" s="20">
+        <v>2532165400</v>
+      </c>
+      <c r="I158" s="20">
+        <v>567639839</v>
+      </c>
+      <c r="J158" s="20" t="s">
+        <v>511</v>
+      </c>
+      <c r="K158" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="L158" s="20" t="s">
+        <v>514</v>
+      </c>
+      <c r="M158" s="23" t="s">
         <v>515</v>
       </c>
-      <c r="H158" s="20">
-        <v>2611973781</v>
-      </c>
-      <c r="I158" s="20">
-        <v>538841925</v>
-      </c>
-      <c r="J158" s="20" t="s">
-        <v>521</v>
-      </c>
-      <c r="K158" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="L158" s="20" t="s">
-        <v>523</v>
-      </c>
-      <c r="M158" s="23" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="159" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    </row>
+    <row r="159" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A159" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="26"/>
         <v>154</v>
       </c>
       <c r="B159" s="20" t="s">
-        <v>511</v>
+        <v>501</v>
       </c>
       <c r="C159" s="3"/>
       <c r="D159" s="20" t="s">
-        <v>512</v>
+        <v>503</v>
       </c>
       <c r="E159" s="20" t="s">
         <v>48</v>
       </c>
       <c r="F159" s="18">
-        <v>45682</v>
+        <v>45684</v>
       </c>
       <c r="G159" s="20" t="s">
-        <v>516</v>
+        <v>508</v>
       </c>
       <c r="H159" s="20">
-        <v>2558563686</v>
+        <v>2390951701</v>
       </c>
       <c r="I159" s="20">
-        <v>549803297</v>
+        <v>592939288</v>
       </c>
       <c r="J159" s="20" t="s">
-        <v>521</v>
+        <v>511</v>
       </c>
       <c r="K159" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L159" s="20" t="s">
-        <v>523</v>
+        <v>514</v>
       </c>
       <c r="M159" s="23" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="160" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="160" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="26"/>
         <v>155</v>
       </c>
       <c r="B160" s="20" t="s">
-        <v>511</v>
-      </c>
-      <c r="C160" s="3"/>
+        <v>501</v>
+      </c>
+      <c r="C160" s="17"/>
       <c r="D160" s="20" t="s">
-        <v>513</v>
+        <v>504</v>
       </c>
       <c r="E160" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="F160" s="18">
-        <v>45683</v>
-      </c>
+      <c r="F160" s="17"/>
       <c r="G160" s="20" t="s">
-        <v>517</v>
+        <v>509</v>
       </c>
       <c r="H160" s="20">
-        <v>2532165400</v>
+        <v>2618345389</v>
       </c>
       <c r="I160" s="20">
-        <v>567639839</v>
+        <v>598308187</v>
       </c>
       <c r="J160" s="20" t="s">
-        <v>521</v>
+        <v>512</v>
       </c>
       <c r="K160" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L160" s="20" t="s">
-        <v>524</v>
+        <v>514</v>
       </c>
       <c r="M160" s="23" t="s">
-        <v>525</v>
+        <v>515</v>
       </c>
     </row>
     <row r="161" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A161" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="26"/>
         <v>156</v>
       </c>
       <c r="B161" s="20" t="s">
-        <v>511</v>
-      </c>
-      <c r="C161" s="3"/>
+        <v>501</v>
+      </c>
+      <c r="C161" s="17"/>
       <c r="D161" s="20" t="s">
-        <v>513</v>
+        <v>504</v>
       </c>
       <c r="E161" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="F161" s="18">
-        <v>45684</v>
-      </c>
+      <c r="F161" s="17"/>
       <c r="G161" s="20" t="s">
-        <v>518</v>
+        <v>510</v>
       </c>
       <c r="H161" s="20">
-        <v>2390951701</v>
+        <v>2506550348</v>
       </c>
       <c r="I161" s="20">
-        <v>592939288</v>
+        <v>534729954</v>
       </c>
       <c r="J161" s="20" t="s">
-        <v>521</v>
+        <v>512</v>
       </c>
       <c r="K161" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L161" s="20" t="s">
-        <v>524</v>
+        <v>514</v>
       </c>
       <c r="M161" s="23" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="162" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="162" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A162" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="26"/>
         <v>157</v>
       </c>
       <c r="B162" s="20" t="s">
-        <v>511</v>
+        <v>501</v>
       </c>
       <c r="C162" s="17"/>
       <c r="D162" s="20" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="E162" s="20" t="s">
         <v>15</v>
       </c>
       <c r="F162" s="17"/>
       <c r="G162" s="20" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H162" s="20">
-        <v>2618345389</v>
-      </c>
-      <c r="I162" s="20">
-        <v>598308187</v>
+        <v>2504168259</v>
+      </c>
+      <c r="I162" s="20" t="s">
+        <v>522</v>
       </c>
       <c r="J162" s="20" t="s">
-        <v>522</v>
+        <v>511</v>
       </c>
       <c r="K162" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L162" s="20" t="s">
-        <v>524</v>
+        <v>476</v>
       </c>
       <c r="M162" s="23" t="s">
-        <v>525</v>
+        <v>515</v>
       </c>
     </row>
     <row r="163" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A163" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="26"/>
         <v>158</v>
       </c>
       <c r="B163" s="20" t="s">
-        <v>511</v>
+        <v>501</v>
       </c>
       <c r="C163" s="17"/>
       <c r="D163" s="20" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="E163" s="20" t="s">
         <v>48</v>
       </c>
       <c r="F163" s="17"/>
       <c r="G163" s="20" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H163" s="20">
-        <v>2506550348</v>
+        <v>2556157374</v>
       </c>
       <c r="I163" s="20">
-        <v>534729954</v>
+        <v>595630483</v>
       </c>
       <c r="J163" s="20" t="s">
-        <v>522</v>
+        <v>511</v>
       </c>
       <c r="K163" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L163" s="20" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="M163" s="23" t="s">
-        <v>525</v>
+        <v>515</v>
       </c>
     </row>
     <row r="164" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A164" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="26"/>
         <v>159</v>
       </c>
       <c r="B164" s="20" t="s">
-        <v>511</v>
+        <v>501</v>
       </c>
       <c r="C164" s="17"/>
       <c r="D164" s="20" t="s">
-        <v>526</v>
+        <v>517</v>
       </c>
       <c r="E164" s="20" t="s">
         <v>15</v>
       </c>
       <c r="F164" s="17"/>
       <c r="G164" s="20" t="s">
-        <v>528</v>
+        <v>520</v>
       </c>
       <c r="H164" s="20">
-        <v>2504168259</v>
-      </c>
-      <c r="I164" s="20" t="s">
-        <v>532</v>
+        <v>2596928115</v>
+      </c>
+      <c r="I164" s="20">
+        <v>569819068</v>
       </c>
       <c r="J164" s="20" t="s">
-        <v>521</v>
+        <v>512</v>
       </c>
       <c r="K164" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L164" s="20" t="s">
-        <v>487</v>
+        <v>476</v>
       </c>
       <c r="M164" s="23" t="s">
-        <v>525</v>
+        <v>515</v>
       </c>
     </row>
     <row r="165" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A165" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="26"/>
         <v>160</v>
       </c>
       <c r="B165" s="20" t="s">
-        <v>511</v>
+        <v>501</v>
       </c>
       <c r="C165" s="17"/>
       <c r="D165" s="20" t="s">
-        <v>526</v>
+        <v>517</v>
       </c>
       <c r="E165" s="20" t="s">
         <v>48</v>
       </c>
       <c r="F165" s="17"/>
       <c r="G165" s="20" t="s">
-        <v>529</v>
+        <v>521</v>
       </c>
       <c r="H165" s="20">
-        <v>2556157374</v>
+        <v>2601746106</v>
       </c>
       <c r="I165" s="20">
-        <v>595630483</v>
+        <v>595093247</v>
       </c>
       <c r="J165" s="20" t="s">
-        <v>521</v>
+        <v>512</v>
       </c>
       <c r="K165" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L165" s="20" t="s">
-        <v>533</v>
+        <v>476</v>
       </c>
       <c r="M165" s="23" t="s">
-        <v>525</v>
+        <v>515</v>
       </c>
     </row>
     <row r="166" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A166" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="26"/>
         <v>161</v>
       </c>
       <c r="B166" s="20" t="s">
-        <v>511</v>
+        <v>379</v>
       </c>
       <c r="C166" s="17"/>
       <c r="D166" s="20" t="s">
-        <v>527</v>
-      </c>
-      <c r="E166" s="20" t="s">
-        <v>15</v>
+        <v>526</v>
+      </c>
+      <c r="E166" s="17" t="s">
+        <v>10</v>
       </c>
       <c r="F166" s="17"/>
       <c r="G166" s="20" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="H166" s="20">
-        <v>2596928115</v>
+        <v>2411929983</v>
       </c>
       <c r="I166" s="20">
-        <v>569819068</v>
+        <v>532849684</v>
       </c>
       <c r="J166" s="20" t="s">
-        <v>522</v>
+        <v>532</v>
       </c>
       <c r="K166" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L166" s="20" t="s">
-        <v>487</v>
+        <v>533</v>
       </c>
       <c r="M166" s="23" t="s">
-        <v>525</v>
+        <v>515</v>
       </c>
     </row>
     <row r="167" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A167" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="26"/>
         <v>162</v>
       </c>
       <c r="B167" s="20" t="s">
-        <v>511</v>
+        <v>379</v>
       </c>
       <c r="C167" s="17"/>
       <c r="D167" s="20" t="s">
-        <v>527</v>
-      </c>
-      <c r="E167" s="20" t="s">
-        <v>48</v>
+        <v>526</v>
+      </c>
+      <c r="E167" s="17" t="s">
+        <v>5</v>
       </c>
       <c r="F167" s="17"/>
       <c r="G167" s="20" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="H167" s="20">
-        <v>2601746106</v>
+        <v>2411930163</v>
       </c>
       <c r="I167" s="20">
-        <v>595093247</v>
+        <v>537967849</v>
       </c>
       <c r="J167" s="20" t="s">
-        <v>522</v>
+        <v>532</v>
       </c>
       <c r="K167" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L167" s="20" t="s">
-        <v>487</v>
+        <v>533</v>
       </c>
       <c r="M167" s="23" t="s">
-        <v>525</v>
+        <v>515</v>
       </c>
     </row>
     <row r="168" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A168" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="26"/>
         <v>163</v>
       </c>
       <c r="B168" s="20" t="s">
-        <v>390</v>
-      </c>
-      <c r="C168" s="17"/>
+        <v>379</v>
+      </c>
+      <c r="C168" s="13"/>
       <c r="D168" s="20" t="s">
-        <v>536</v>
+        <v>527</v>
       </c>
       <c r="E168" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="F168" s="17"/>
+        <v>5</v>
+      </c>
+      <c r="F168" s="14"/>
       <c r="G168" s="20" t="s">
-        <v>538</v>
+        <v>530</v>
       </c>
       <c r="H168" s="20">
-        <v>2411929983</v>
+        <v>2614096101</v>
       </c>
       <c r="I168" s="20">
-        <v>532849684</v>
+        <v>569063428</v>
       </c>
       <c r="J168" s="20" t="s">
-        <v>542</v>
+        <v>532</v>
       </c>
       <c r="K168" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L168" s="20" t="s">
-        <v>543</v>
+        <v>533</v>
       </c>
       <c r="M168" s="23" t="s">
-        <v>525</v>
+        <v>515</v>
       </c>
     </row>
     <row r="169" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A169" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="26"/>
         <v>164</v>
       </c>
       <c r="B169" s="20" t="s">
-        <v>390</v>
-      </c>
-      <c r="C169" s="17"/>
+        <v>379</v>
+      </c>
+      <c r="C169" s="13"/>
       <c r="D169" s="20" t="s">
-        <v>536</v>
+        <v>527</v>
       </c>
       <c r="E169" s="17" t="s">
-        <v>5</v>
-      </c>
-      <c r="F169" s="17"/>
+        <v>10</v>
+      </c>
+      <c r="F169" s="14"/>
       <c r="G169" s="20" t="s">
-        <v>539</v>
+        <v>531</v>
       </c>
       <c r="H169" s="20">
-        <v>2411930163</v>
+        <v>2127405435</v>
       </c>
       <c r="I169" s="20">
-        <v>537967849</v>
+        <v>535032649</v>
       </c>
       <c r="J169" s="20" t="s">
-        <v>542</v>
+        <v>532</v>
       </c>
       <c r="K169" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L169" s="20" t="s">
-        <v>543</v>
+        <v>533</v>
       </c>
       <c r="M169" s="23" t="s">
-        <v>525</v>
+        <v>515</v>
       </c>
     </row>
     <row r="170" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A170" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="26"/>
         <v>165</v>
       </c>
-      <c r="B170" s="20" t="s">
-        <v>390</v>
+      <c r="B170" s="3" t="s">
+        <v>466</v>
       </c>
       <c r="C170" s="13"/>
       <c r="D170" s="20" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="E170" s="17" t="s">
-        <v>5</v>
+        <v>535</v>
       </c>
       <c r="F170" s="14"/>
-      <c r="G170" s="20" t="s">
-        <v>540</v>
-      </c>
-      <c r="H170" s="20">
-        <v>2614096101</v>
-      </c>
-      <c r="I170" s="20">
-        <v>569063428</v>
-      </c>
-      <c r="J170" s="20" t="s">
-        <v>542</v>
+      <c r="G170" s="22" t="s">
+        <v>536</v>
+      </c>
+      <c r="H170" s="22">
+        <v>2619138866</v>
+      </c>
+      <c r="I170" s="13"/>
+      <c r="J170" s="3" t="s">
+        <v>138</v>
       </c>
       <c r="K170" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L170" s="20" t="s">
-        <v>543</v>
-      </c>
-      <c r="M170" s="23" t="s">
-        <v>525</v>
+        <v>476</v>
+      </c>
+      <c r="M170" s="24" t="s">
+        <v>515</v>
       </c>
     </row>
     <row r="171" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A171" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="26"/>
         <v>166</v>
       </c>
-      <c r="B171" s="20" t="s">
-        <v>390</v>
+      <c r="B171" s="3" t="s">
+        <v>466</v>
       </c>
       <c r="C171" s="13"/>
       <c r="D171" s="20" t="s">
+        <v>534</v>
+      </c>
+      <c r="E171" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="F171" s="14"/>
+      <c r="G171" s="22" t="s">
         <v>537</v>
       </c>
-      <c r="E171" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="F171" s="14"/>
-      <c r="G171" s="20" t="s">
-        <v>541</v>
-      </c>
-      <c r="H171" s="20">
-        <v>2127405435</v>
-      </c>
-      <c r="I171" s="20">
-        <v>535032649</v>
-      </c>
-      <c r="J171" s="20" t="s">
-        <v>542</v>
+      <c r="H171" s="22">
+        <v>2566626228</v>
+      </c>
+      <c r="I171" s="22">
+        <v>537086275</v>
+      </c>
+      <c r="J171" s="3" t="s">
+        <v>138</v>
       </c>
       <c r="K171" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L171" s="20" t="s">
-        <v>543</v>
-      </c>
-      <c r="M171" s="23" t="s">
-        <v>525</v>
+        <v>476</v>
+      </c>
+      <c r="M171" s="24" t="s">
+        <v>515</v>
       </c>
     </row>
     <row r="172" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A172" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="26"/>
         <v>167</v>
       </c>
       <c r="B172" s="3" t="s">
-        <v>477</v>
+        <v>148</v>
       </c>
       <c r="C172" s="13"/>
-      <c r="D172" s="20" t="s">
-        <v>544</v>
-      </c>
-      <c r="E172" s="17" t="s">
-        <v>545</v>
+      <c r="D172" s="25" t="s">
+        <v>538</v>
+      </c>
+      <c r="E172" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F172" s="14"/>
-      <c r="G172" s="22" t="s">
-        <v>546</v>
-      </c>
-      <c r="H172" s="22">
-        <v>2619138866</v>
-      </c>
-      <c r="I172" s="13"/>
+      <c r="G172" s="25" t="s">
+        <v>539</v>
+      </c>
+      <c r="H172" s="25">
+        <v>2599214000</v>
+      </c>
+      <c r="I172" s="25">
+        <v>597962916</v>
+      </c>
       <c r="J172" s="3" t="s">
-        <v>147</v>
+        <v>43</v>
       </c>
       <c r="K172" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="L172" s="20" t="s">
-        <v>487</v>
-      </c>
-      <c r="M172" s="24" t="s">
-        <v>525</v>
+      <c r="L172" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="M172" s="1" t="s">
+        <v>462</v>
       </c>
     </row>
     <row r="173" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A173" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="26"/>
         <v>168</v>
       </c>
-      <c r="B173" s="3" t="s">
-        <v>477</v>
+      <c r="B173" s="17" t="s">
+        <v>540</v>
       </c>
       <c r="C173" s="13"/>
-      <c r="D173" s="20" t="s">
-        <v>544</v>
-      </c>
-      <c r="E173" s="17" t="s">
+      <c r="D173" s="17" t="s">
+        <v>541</v>
+      </c>
+      <c r="E173" s="3" t="s">
         <v>5</v>
       </c>
       <c r="F173" s="14"/>
-      <c r="G173" s="22" t="s">
-        <v>547</v>
-      </c>
-      <c r="H173" s="22">
-        <v>2566626228</v>
-      </c>
-      <c r="I173" s="22">
-        <v>537086275</v>
-      </c>
+      <c r="G173" s="25"/>
+      <c r="H173" s="25"/>
+      <c r="I173" s="25"/>
       <c r="J173" s="3" t="s">
-        <v>147</v>
+        <v>214</v>
       </c>
       <c r="K173" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="L173" s="20" t="s">
-        <v>487</v>
-      </c>
-      <c r="M173" s="24" t="s">
-        <v>525</v>
+      <c r="L173" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="M173" s="17" t="s">
+        <v>491</v>
       </c>
     </row>
     <row r="174" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A174" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="26"/>
         <v>169</v>
       </c>
-      <c r="B174" s="3" t="s">
-        <v>157</v>
+      <c r="B174" s="17" t="s">
+        <v>540</v>
       </c>
       <c r="C174" s="13"/>
-      <c r="D174" s="25" t="s">
-        <v>548</v>
-      </c>
-      <c r="E174" s="3" t="s">
-        <v>5</v>
+      <c r="D174" s="17" t="s">
+        <v>541</v>
+      </c>
+      <c r="E174" s="17" t="s">
+        <v>10</v>
       </c>
       <c r="F174" s="14"/>
-      <c r="G174" s="25" t="s">
-        <v>549</v>
-      </c>
-      <c r="H174" s="25">
-        <v>2599214000</v>
-      </c>
-      <c r="I174" s="25">
-        <v>597962916</v>
-      </c>
+      <c r="G174" s="13"/>
+      <c r="H174" s="13"/>
+      <c r="I174" s="13"/>
       <c r="J174" s="3" t="s">
-        <v>43</v>
+        <v>214</v>
       </c>
       <c r="K174" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L174" s="3" t="s">
-        <v>423</v>
-      </c>
-      <c r="M174" s="1" t="s">
-        <v>473</v>
+        <v>412</v>
+      </c>
+      <c r="M174" s="17" t="s">
+        <v>491</v>
       </c>
     </row>
     <row r="175" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A175" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="26"/>
         <v>170</v>
       </c>
-      <c r="B175" s="13"/>
+      <c r="B175" s="17" t="s">
+        <v>540</v>
+      </c>
       <c r="C175" s="13"/>
-      <c r="D175" s="13"/>
-      <c r="E175" s="13"/>
+      <c r="D175" s="17" t="s">
+        <v>542</v>
+      </c>
+      <c r="E175" s="3" t="s">
+        <v>5</v>
+      </c>
       <c r="F175" s="14"/>
       <c r="G175" s="13"/>
       <c r="H175" s="13"/>
       <c r="I175" s="13"/>
-      <c r="J175" s="13"/>
-      <c r="K175" s="3"/>
-      <c r="L175" s="13"/>
-      <c r="M175" s="13"/>
+      <c r="J175" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="K175" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="L175" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="M175" s="17" t="s">
+        <v>491</v>
+      </c>
     </row>
     <row r="176" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A176" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="26"/>
         <v>171</v>
       </c>
-      <c r="B176" s="13"/>
+      <c r="B176" s="17" t="s">
+        <v>540</v>
+      </c>
       <c r="C176" s="13"/>
-      <c r="D176" s="13"/>
-      <c r="E176" s="13"/>
+      <c r="D176" s="17" t="s">
+        <v>542</v>
+      </c>
+      <c r="E176" s="17" t="s">
+        <v>10</v>
+      </c>
       <c r="F176" s="14"/>
       <c r="G176" s="13"/>
       <c r="H176" s="13"/>
       <c r="I176" s="13"/>
-      <c r="J176" s="13"/>
-      <c r="K176" s="3"/>
-      <c r="L176" s="13"/>
-      <c r="M176" s="13"/>
+      <c r="J176" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="K176" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="L176" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="M176" s="17" t="s">
+        <v>491</v>
+      </c>
     </row>
     <row r="177" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A177" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="26"/>
         <v>172</v>
       </c>
-      <c r="B177" s="13"/>
+      <c r="B177" s="12" t="s">
+        <v>543</v>
+      </c>
       <c r="C177" s="13"/>
-      <c r="D177" s="13"/>
-      <c r="E177" s="13"/>
+      <c r="D177" s="15" t="s">
+        <v>544</v>
+      </c>
+      <c r="E177" s="3" t="s">
+        <v>5</v>
+      </c>
       <c r="F177" s="14"/>
-      <c r="G177" s="13"/>
-      <c r="H177" s="13"/>
-      <c r="I177" s="13"/>
-      <c r="J177" s="13"/>
-      <c r="K177" s="3"/>
-      <c r="L177" s="13"/>
-      <c r="M177" s="13"/>
+      <c r="G177" s="15" t="s">
+        <v>284</v>
+      </c>
+      <c r="H177" s="17">
+        <v>2619815406</v>
+      </c>
+      <c r="I177" s="17">
+        <v>530268978</v>
+      </c>
+      <c r="J177" s="17" t="s">
+        <v>547</v>
+      </c>
+      <c r="K177" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="L177" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="M177" s="17" t="s">
+        <v>548</v>
+      </c>
     </row>
     <row r="178" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A178" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="26"/>
         <v>173</v>
       </c>
-      <c r="B178" s="13"/>
+      <c r="B178" s="12" t="s">
+        <v>543</v>
+      </c>
       <c r="C178" s="13"/>
-      <c r="D178" s="13"/>
-      <c r="E178" s="13"/>
+      <c r="D178" s="15" t="s">
+        <v>545</v>
+      </c>
+      <c r="E178" s="17" t="s">
+        <v>10</v>
+      </c>
       <c r="F178" s="14"/>
-      <c r="G178" s="13"/>
-      <c r="H178" s="13"/>
-      <c r="I178" s="13"/>
-      <c r="J178" s="13"/>
-      <c r="K178" s="3"/>
-      <c r="L178" s="13"/>
-      <c r="M178" s="13"/>
+      <c r="G178" s="15" t="s">
+        <v>546</v>
+      </c>
+      <c r="H178" s="17">
+        <v>2373476924</v>
+      </c>
+      <c r="I178" s="17">
+        <v>583369309</v>
+      </c>
+      <c r="J178" s="17" t="s">
+        <v>547</v>
+      </c>
+      <c r="K178" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="L178" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="M178" s="17" t="s">
+        <v>548</v>
+      </c>
     </row>
     <row r="179" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A179" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="26"/>
         <v>174</v>
       </c>
       <c r="B179" s="13"/>
       <c r="C179" s="13"/>
-      <c r="D179" s="13"/>
+      <c r="D179" s="17"/>
       <c r="E179" s="13"/>
       <c r="F179" s="14"/>
       <c r="G179" s="13"/>
@@ -9698,7 +9752,7 @@
     </row>
     <row r="180" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A180" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="26"/>
         <v>175</v>
       </c>
       <c r="B180" s="13"/>
@@ -9716,7 +9770,7 @@
     </row>
     <row r="181" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A181" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="26"/>
         <v>176</v>
       </c>
       <c r="B181" s="13"/>
@@ -9734,7 +9788,7 @@
     </row>
     <row r="182" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A182" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="26"/>
         <v>177</v>
       </c>
       <c r="B182" s="13"/>
@@ -9752,7 +9806,7 @@
     </row>
     <row r="183" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A183" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="A183:A187" si="27">A182+1</f>
         <v>178</v>
       </c>
       <c r="B183" s="13"/>
@@ -9770,7 +9824,7 @@
     </row>
     <row r="184" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A184" s="11">
-        <f t="shared" ref="A184:A199" si="4">A183+1</f>
+        <f t="shared" si="27"/>
         <v>179</v>
       </c>
       <c r="B184" s="13"/>
@@ -9788,7 +9842,7 @@
     </row>
     <row r="185" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A185" s="11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="27"/>
         <v>180</v>
       </c>
       <c r="B185" s="13"/>
@@ -9806,7 +9860,7 @@
     </row>
     <row r="186" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A186" s="11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="27"/>
         <v>181</v>
       </c>
       <c r="B186" s="13"/>
@@ -9824,7 +9878,7 @@
     </row>
     <row r="187" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A187" s="11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="27"/>
         <v>182</v>
       </c>
       <c r="B187" s="13"/>
@@ -9836,13 +9890,13 @@
       <c r="H187" s="13"/>
       <c r="I187" s="13"/>
       <c r="J187" s="13"/>
-      <c r="K187" s="3"/>
+      <c r="K187" s="15"/>
       <c r="L187" s="13"/>
       <c r="M187" s="13"/>
     </row>
     <row r="188" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A188" s="11">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="A188:A198" si="28">A187+1</f>
         <v>183</v>
       </c>
       <c r="B188" s="13"/>
@@ -9860,7 +9914,7 @@
     </row>
     <row r="189" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A189" s="11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="28"/>
         <v>184</v>
       </c>
       <c r="B189" s="13"/>
@@ -9878,7 +9932,7 @@
     </row>
     <row r="190" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A190" s="11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="28"/>
         <v>185</v>
       </c>
       <c r="B190" s="13"/>
@@ -9896,7 +9950,7 @@
     </row>
     <row r="191" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A191" s="11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="28"/>
         <v>186</v>
       </c>
       <c r="B191" s="13"/>
@@ -9914,7 +9968,7 @@
     </row>
     <row r="192" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A192" s="11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="28"/>
         <v>187</v>
       </c>
       <c r="B192" s="13"/>
@@ -9932,7 +9986,7 @@
     </row>
     <row r="193" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A193" s="11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="28"/>
         <v>188</v>
       </c>
       <c r="B193" s="13"/>
@@ -9950,7 +10004,7 @@
     </row>
     <row r="194" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A194" s="11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="28"/>
         <v>189</v>
       </c>
       <c r="B194" s="13"/>
@@ -9968,7 +10022,7 @@
     </row>
     <row r="195" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A195" s="11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="28"/>
         <v>190</v>
       </c>
       <c r="B195" s="13"/>
@@ -9986,7 +10040,7 @@
     </row>
     <row r="196" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A196" s="11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="28"/>
         <v>191</v>
       </c>
       <c r="B196" s="13"/>
@@ -10004,7 +10058,7 @@
     </row>
     <row r="197" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A197" s="11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="28"/>
         <v>192</v>
       </c>
       <c r="B197" s="13"/>
@@ -10022,7 +10076,7 @@
     </row>
     <row r="198" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A198" s="11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="28"/>
         <v>193</v>
       </c>
       <c r="B198" s="13"/>
@@ -10038,11 +10092,7 @@
       <c r="L198" s="13"/>
       <c r="M198" s="13"/>
     </row>
-    <row r="199" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A199" s="11">
-        <f t="shared" si="4"/>
-        <v>194</v>
-      </c>
+    <row r="199" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B199" s="13"/>
       <c r="C199" s="13"/>
       <c r="D199" s="13"/>
@@ -13038,139 +13088,156 @@
       <c r="L412" s="13"/>
       <c r="M412" s="13"/>
     </row>
-    <row r="413" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B413" s="13"/>
-      <c r="C413" s="13"/>
-      <c r="D413" s="13"/>
-      <c r="E413" s="13"/>
-      <c r="F413" s="14"/>
-      <c r="G413" s="13"/>
-      <c r="H413" s="13"/>
-      <c r="I413" s="13"/>
-      <c r="J413" s="13"/>
-      <c r="K413" s="15"/>
-      <c r="L413" s="13"/>
-      <c r="M413" s="13"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:M199" xr:uid="{9AEAC16E-221F-49E8-9C2A-7CA8F46B2CE6}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M38">
-      <sortCondition ref="B1:B37"/>
+  <autoFilter ref="A1:M198" xr:uid="{9AEAC16E-221F-49E8-9C2A-7CA8F46B2CE6}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M36">
+      <sortCondition ref="B1:B35"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="2" type="noConversion"/>
-  <conditionalFormatting sqref="D139:D145">
-    <cfRule type="duplicateValues" dxfId="36" priority="35"/>
+  <conditionalFormatting sqref="D137:D143">
+    <cfRule type="duplicateValues" dxfId="36" priority="36"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G34:G46">
-    <cfRule type="duplicateValues" dxfId="35" priority="256"/>
+  <conditionalFormatting sqref="G32:G44">
+    <cfRule type="duplicateValues" dxfId="35" priority="257"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G147:G148 G47:G138">
-    <cfRule type="duplicateValues" dxfId="34" priority="433"/>
+  <conditionalFormatting sqref="G145:G146 G45:G72 G74:G136">
+    <cfRule type="duplicateValues" dxfId="34" priority="434"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G175:G1048576 G147:G149 G1:G22 G24:G138">
-    <cfRule type="duplicateValues" dxfId="33" priority="238"/>
+  <conditionalFormatting sqref="G174:G1048576 G145:G147 G1:G20 G22:G72 G74:G136">
+    <cfRule type="duplicateValues" dxfId="33" priority="239"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G175:G1048576 G149 G1:G22 G24:G33">
-    <cfRule type="duplicateValues" dxfId="32" priority="451"/>
+  <conditionalFormatting sqref="G174:G1048576 G147 G1:G20 G22:G31">
+    <cfRule type="duplicateValues" dxfId="32" priority="452"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H14:H17">
-    <cfRule type="duplicateValues" dxfId="31" priority="249"/>
+  <conditionalFormatting sqref="H32:H44">
+    <cfRule type="duplicateValues" dxfId="31" priority="255"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H34:H46">
-    <cfRule type="duplicateValues" dxfId="30" priority="254"/>
+  <conditionalFormatting sqref="H145:H146 H45:H136">
+    <cfRule type="duplicateValues" dxfId="30" priority="436"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H147:H148 H47:H138">
-    <cfRule type="duplicateValues" dxfId="29" priority="435"/>
+  <conditionalFormatting sqref="I147 I137:I144">
+    <cfRule type="duplicateValues" dxfId="29" priority="35"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I149 I139:I146">
+  <conditionalFormatting sqref="G148:G153">
     <cfRule type="duplicateValues" dxfId="28" priority="34"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G150:G155">
-    <cfRule type="duplicateValues" dxfId="27" priority="33"/>
+  <conditionalFormatting sqref="H148:H153">
+    <cfRule type="duplicateValues" dxfId="27" priority="32"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H150:H155">
-    <cfRule type="duplicateValues" dxfId="26" priority="31"/>
+  <conditionalFormatting sqref="H148:H153">
+    <cfRule type="duplicateValues" dxfId="26" priority="33"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H150:H155">
-    <cfRule type="duplicateValues" dxfId="25" priority="32"/>
+  <conditionalFormatting sqref="G154:G155">
+    <cfRule type="duplicateValues" dxfId="25" priority="31"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G156:G157">
-    <cfRule type="duplicateValues" dxfId="24" priority="30"/>
+  <conditionalFormatting sqref="H154:H155">
+    <cfRule type="duplicateValues" dxfId="24" priority="29"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H156:H157">
-    <cfRule type="duplicateValues" dxfId="23" priority="28"/>
+  <conditionalFormatting sqref="H154:H155">
+    <cfRule type="duplicateValues" dxfId="23" priority="30"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H156:H157">
-    <cfRule type="duplicateValues" dxfId="22" priority="29"/>
+  <conditionalFormatting sqref="G156:G161">
+    <cfRule type="duplicateValues" dxfId="22" priority="28"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G158:G163">
-    <cfRule type="duplicateValues" dxfId="21" priority="27"/>
+  <conditionalFormatting sqref="H156:H161">
+    <cfRule type="duplicateValues" dxfId="21" priority="26"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H158:H163">
-    <cfRule type="duplicateValues" dxfId="20" priority="25"/>
+  <conditionalFormatting sqref="H156:H161">
+    <cfRule type="duplicateValues" dxfId="20" priority="27"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H158:H163">
-    <cfRule type="duplicateValues" dxfId="19" priority="26"/>
+  <conditionalFormatting sqref="G162:G165">
+    <cfRule type="duplicateValues" dxfId="19" priority="25"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G164:G167">
-    <cfRule type="duplicateValues" dxfId="18" priority="24"/>
+  <conditionalFormatting sqref="H162:H165">
+    <cfRule type="duplicateValues" dxfId="18" priority="23"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H164:H167">
-    <cfRule type="duplicateValues" dxfId="17" priority="22"/>
+  <conditionalFormatting sqref="H162:H165">
+    <cfRule type="duplicateValues" dxfId="17" priority="24"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H164:H167">
-    <cfRule type="duplicateValues" dxfId="16" priority="23"/>
+  <conditionalFormatting sqref="H16:H17">
+    <cfRule type="duplicateValues" dxfId="16" priority="460"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H18:H19">
-    <cfRule type="duplicateValues" dxfId="15" priority="459"/>
+  <conditionalFormatting sqref="H18:H20 H22:H31">
+    <cfRule type="duplicateValues" dxfId="15" priority="488"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H20:H22 H24:H33">
-    <cfRule type="duplicateValues" dxfId="14" priority="487"/>
+  <conditionalFormatting sqref="G21">
+    <cfRule type="duplicateValues" dxfId="14" priority="20"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G23">
-    <cfRule type="duplicateValues" dxfId="13" priority="19"/>
+  <conditionalFormatting sqref="H21">
+    <cfRule type="duplicateValues" dxfId="13" priority="21"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H23">
-    <cfRule type="duplicateValues" dxfId="12" priority="20"/>
+  <conditionalFormatting sqref="H21">
+    <cfRule type="duplicateValues" dxfId="12" priority="22"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H23">
-    <cfRule type="duplicateValues" dxfId="11" priority="21"/>
+  <conditionalFormatting sqref="G166:G169">
+    <cfRule type="duplicateValues" dxfId="11" priority="16"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G168:G171">
-    <cfRule type="duplicateValues" dxfId="10" priority="15"/>
+  <conditionalFormatting sqref="H166:H169">
+    <cfRule type="duplicateValues" dxfId="10" priority="17"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H168:H171">
-    <cfRule type="duplicateValues" dxfId="9" priority="16"/>
+  <conditionalFormatting sqref="I166:I167">
+    <cfRule type="duplicateValues" dxfId="9" priority="19"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I168:I169">
+  <conditionalFormatting sqref="H166:H169">
     <cfRule type="duplicateValues" dxfId="8" priority="18"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H168:H171">
-    <cfRule type="duplicateValues" dxfId="7" priority="17"/>
+  <conditionalFormatting sqref="G170:G171">
+    <cfRule type="duplicateValues" dxfId="7" priority="7"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G172:G173">
-    <cfRule type="duplicateValues" dxfId="6" priority="6"/>
+  <conditionalFormatting sqref="G170:G171">
+    <cfRule type="duplicateValues" dxfId="6" priority="8"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G172:G173">
-    <cfRule type="duplicateValues" dxfId="5" priority="7"/>
+  <conditionalFormatting sqref="H170">
+    <cfRule type="duplicateValues" dxfId="5" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H172">
-    <cfRule type="duplicateValues" dxfId="4" priority="4"/>
+  <conditionalFormatting sqref="H170">
+    <cfRule type="duplicateValues" dxfId="4" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H172">
-    <cfRule type="duplicateValues" dxfId="3" priority="5"/>
+  <conditionalFormatting sqref="H171">
+    <cfRule type="duplicateValues" dxfId="3" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H173">
-    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
+  <conditionalFormatting sqref="H171">
+    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H173">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+  <conditionalFormatting sqref="I171">
+    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I173">
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+  <conditionalFormatting sqref="G73">
+    <cfRule type="dataBar" priority="1">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{2AE2CA6C-4AA1-41E8-89B9-DB7B36C0C2F2}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H13:H15">
+    <cfRule type="duplicateValues" dxfId="0" priority="500"/>
   </conditionalFormatting>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="39" fitToHeight="0" orientation="landscape" verticalDpi="0" r:id="rId1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
+      <x14:conditionalFormattings>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{2AE2CA6C-4AA1-41E8-89B9-DB7B36C0C2F2}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>G73</xm:sqref>
+        </x14:conditionalFormatting>
+      </x14:conditionalFormattings>
+    </ext>
+  </extLst>
 </worksheet>
 </file>